--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -878,42 +878,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>16934.062</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>16854.118</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>50.8</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>61794246.37</v>
+        <v>50764557.16</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,32 +1182,32 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>76961261.38</v>
+        <v>61794246.37</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1613,17 +1613,17 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-102649650.64</v>
+        <v>76961261.38</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,32 +2044,32 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
+          <t>-184380592.2611023</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-105526151.13</v>
+        <v>-102649650.64</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9726.752</t>
+          <t>6580.167</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.37</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-14.3</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>59.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-136.15</t>
+          <t>-136.69</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>458810419.0</t>
+          <t>313260581.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>583628887.2</t>
+          <t>531114807.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>529295603.5</t>
+          <t>511080645.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2895834496.86</t>
+          <t>2772797348.26</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>54333283</t>
+          <t>20034161</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-216279783.8905731</t>
+          <t>-199240763.4657515</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-98524978.08</v>
+        <v>-105526151.13</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18985.299</t>
+          <t>9726.752</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>-14.3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>51.78</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>54.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-135.73</t>
+          <t>-136.15</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>907361816.0</t>
+          <t>458810419.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>595612832.4</t>
+          <t>583628887.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>525692219.6</t>
+          <t>529295603.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2953848981.62</t>
+          <t>2895834496.86</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>69920612</t>
+          <t>54333283</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-237689748.5834216</t>
+          <t>-216279783.8905731</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-100599178.58</v>
+        <v>-98524978.08</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,32 +3337,32 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>47.3</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>47.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9234.129</t>
+          <t>18985.299</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,17 +3595,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.94</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>49.98</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>51.78</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>60.42</t>
+          <t>60.17</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>54.19</t>
+          <t>54.31</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-135.56</t>
+          <t>-135.73</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>464487916.0</t>
+          <t>907361816.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>487945910.2</t>
+          <t>595612832.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>469310663.0</t>
+          <t>525692219.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3055293723.54</t>
+          <t>2953848981.62</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>18635247</t>
+          <t>69920612</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-262615306.766223</t>
+          <t>-237689748.5834216</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-148028572.59</v>
+        <v>-100599178.58</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,32 +3768,32 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10271.075</t>
+          <t>9234.129</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-12.86</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>52.26</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>60.42</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>54.03</t>
+          <t>54.19</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-135.86</t>
+          <t>-135.56</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>511653304.0</t>
+          <t>464487916.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>498786728.2</t>
+          <t>487945910.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>463094155.0</t>
+          <t>469310663.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3237534067.52</t>
+          <t>3055293723.54</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>35692573</t>
+          <t>18635247</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-283449258.4345579</t>
+          <t>-262615306.766223</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-163047340.02</v>
+        <v>-148028572.59</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,17 +4199,17 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11439.749</t>
+          <t>10271.075</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-26.37</t>
+          <t>-25.48</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,72 +4457,72 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.86</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>12.22</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>50.72000000000001</t>
+          <t>50.52</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>52.84</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>60.82</t>
+          <t>60.63</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>54.03</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-135.87</t>
+          <t>-135.86</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>575830981.0</t>
+          <t>511653304.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>491046483.6</t>
+          <t>498786728.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>466191474.3</t>
+          <t>463094155.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3329174084.28</t>
+          <t>3237534067.52</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>24855009</t>
+          <t>35692573</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-305340516.3289255</t>
+          <t>-283449258.4345579</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-183733037.19</v>
+        <v>-163047340.02</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10045.651</t>
+          <t>11439.749</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-26.37</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,17 +4888,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>51.23999999999999</t>
+          <t>50.72000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.92</t>
+          <t>60.82</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-135.67</t>
+          <t>-135.87</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>518730145.0</t>
+          <t>575830981.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>474962319.8</t>
+          <t>491046483.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>458641312.8</t>
+          <t>466191474.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3509950642.14</t>
+          <t>3329174084.28</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>16321007</t>
+          <t>24855009</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-327450967.0807714</t>
+          <t>-305340516.3289255</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-213598318.66</v>
+        <v>-183733037.19</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7274.055</t>
+          <t>10045.651</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-25.19</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.67</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.81</t>
+          <t>-11.35</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>51.34</t>
+          <t>51.23999999999999</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>54.42</t>
+          <t>54.01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>60.92</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>53.54</t>
+          <t>53.71</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-7.60</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-135.52</t>
+          <t>-135.67</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1140188802.401592</t>
+          <t>1140443624.577312</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>369027205.0</t>
+          <t>518730145.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>455771606.8</t>
+          <t>474962319.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>478360854.2</t>
+          <t>458641312.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3627840142.66</t>
+          <t>3509950642.14</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-22589247</t>
+          <t>16321007</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-348151448.6125913</t>
+          <t>-327450967.0807714</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-242516548.36</v>
+        <v>-213598318.66</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>80.85019803591774</t>
+          <t>-36.86822403006653</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>30.9975879466106</t>
+          <t>-14.58459224643812</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>1.10499235356195</t>
+          <t>-2.04560003730758</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>29.36</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,67 +1009,67 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>57.56</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1030169557.8</t>
+          <t>1149525583.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1957468999.34</t>
+          <t>1776903570.96</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>50764557.16</v>
+        <v>44201426.71</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>61794246.37</v>
+        <v>50764557.16</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>76961261.38</v>
+        <v>61794246.37</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-102649650.64</v>
+        <v>76961261.38</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
+          <t>-184380592.2611023</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-105526151.13</v>
+        <v>-102649650.64</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9726.752</t>
+          <t>6580.167</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.37</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-14.3</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>59.59</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-136.15</t>
+          <t>-136.69</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>458810419.0</t>
+          <t>313260581.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>583628887.2</t>
+          <t>531114807.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>529295603.5</t>
+          <t>511080645.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2895834496.86</t>
+          <t>2772797348.26</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>54333283</t>
+          <t>20034161</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-216279783.8905731</t>
+          <t>-199240763.4657515</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-98524978.08</v>
+        <v>-105526151.13</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18985.299</t>
+          <t>9726.752</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>-14.3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>51.78</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>54.43</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-135.73</t>
+          <t>-136.15</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>907361816.0</t>
+          <t>458810419.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>595612832.4</t>
+          <t>583628887.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>525692219.6</t>
+          <t>529295603.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2953848981.62</t>
+          <t>2895834496.86</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>69920612</t>
+          <t>54333283</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-237689748.5834216</t>
+          <t>-216279783.8905731</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-100599178.58</v>
+        <v>-98524978.08</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>47.3</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>47.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9234.129</t>
+          <t>18985.299</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.94</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>49.98</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>51.78</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>60.42</t>
+          <t>60.17</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>54.19</t>
+          <t>54.31</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-135.56</t>
+          <t>-135.73</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>464487916.0</t>
+          <t>907361816.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>487945910.2</t>
+          <t>595612832.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>469310663.0</t>
+          <t>525692219.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>3055293723.54</t>
+          <t>2953848981.62</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>18635247</t>
+          <t>69920612</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-262615306.766223</t>
+          <t>-237689748.5834216</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-148028572.59</v>
+        <v>-100599178.58</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10271.075</t>
+          <t>9234.129</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-12.86</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>52.26</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>60.42</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>54.03</t>
+          <t>54.19</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-135.86</t>
+          <t>-135.56</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>511653304.0</t>
+          <t>464487916.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>498786728.2</t>
+          <t>487945910.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>463094155.0</t>
+          <t>469310663.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3237534067.52</t>
+          <t>3055293723.54</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>35692573</t>
+          <t>18635247</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-283449258.4345579</t>
+          <t>-262615306.766223</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-163047340.02</v>
+        <v>-148028572.59</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11439.749</t>
+          <t>10271.075</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-26.37</t>
+          <t>-25.48</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,72 +4888,72 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.86</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>12.22</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>50.72000000000001</t>
+          <t>50.52</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>52.84</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.82</t>
+          <t>60.63</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>54.03</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-135.87</t>
+          <t>-135.86</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>575830981.0</t>
+          <t>511653304.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>491046483.6</t>
+          <t>498786728.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>466191474.3</t>
+          <t>463094155.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3329174084.28</t>
+          <t>3237534067.52</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>24855009</t>
+          <t>35692573</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-305340516.3289255</t>
+          <t>-283449258.4345579</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-183733037.19</v>
+        <v>-163047340.02</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10045.651</t>
+          <t>11439.749</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-26.37</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,17 +5319,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.35</t>
+          <t>-12.13</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>51.23999999999999</t>
+          <t>50.72000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>53.45</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60.92</t>
+          <t>60.82</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>53.86</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-135.67</t>
+          <t>-135.87</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1140443624.577312</t>
+          <t>1140767747.87013</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>518730145.0</t>
+          <t>575830981.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>474962319.8</t>
+          <t>491046483.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>458641312.8</t>
+          <t>466191474.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3509950642.14</t>
+          <t>3329174084.28</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>16321007</t>
+          <t>24855009</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-327450967.0807714</t>
+          <t>-305340516.3289255</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-213598318.66</v>
+        <v>-183733037.19</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>23.94</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1149525583.8</t>
+          <t>1199384865.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1776903570.96</t>
+          <t>1647059956.98</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>44201426.71</v>
+        <v>17580088.43</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,67 +1440,67 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>57.56</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1030169557.8</t>
+          <t>1149525583.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1957468999.34</t>
+          <t>1776903570.96</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>50764557.16</v>
+        <v>44201426.71</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1698,17 +1698,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>61794246.37</v>
+        <v>50764557.16</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>76961261.38</v>
+        <v>61794246.37</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-102649650.64</v>
+        <v>76961261.38</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
+          <t>-184380592.2611023</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-105526151.13</v>
+        <v>-102649650.64</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9726.752</t>
+          <t>6580.167</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.37</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-14.3</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>59.59</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-136.15</t>
+          <t>-136.69</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>458810419.0</t>
+          <t>313260581.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>583628887.2</t>
+          <t>531114807.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>529295603.5</t>
+          <t>511080645.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2895834496.86</t>
+          <t>2772797348.26</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>54333283</t>
+          <t>20034161</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-216279783.8905731</t>
+          <t>-199240763.4657515</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-98524978.08</v>
+        <v>-105526151.13</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18985.299</t>
+          <t>9726.752</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>-14.3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>51.78</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>54.43</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-135.73</t>
+          <t>-136.15</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>907361816.0</t>
+          <t>458810419.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>595612832.4</t>
+          <t>583628887.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>525692219.6</t>
+          <t>529295603.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2953848981.62</t>
+          <t>2895834496.86</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>69920612</t>
+          <t>54333283</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-237689748.5834216</t>
+          <t>-216279783.8905731</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-100599178.58</v>
+        <v>-98524978.08</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>47.3</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>47.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9234.129</t>
+          <t>18985.299</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,17 +4457,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.94</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>49.98</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>51.78</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>60.42</t>
+          <t>60.17</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>54.19</t>
+          <t>54.31</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-135.56</t>
+          <t>-135.73</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>464487916.0</t>
+          <t>907361816.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>487945910.2</t>
+          <t>595612832.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>469310663.0</t>
+          <t>525692219.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>3055293723.54</t>
+          <t>2953848981.62</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>18635247</t>
+          <t>69920612</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-262615306.766223</t>
+          <t>-237689748.5834216</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-148028572.59</v>
+        <v>-100599178.58</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10271.075</t>
+          <t>9234.129</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-12.86</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>52.26</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>60.42</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>54.03</t>
+          <t>54.19</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-135.86</t>
+          <t>-135.56</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>511653304.0</t>
+          <t>464487916.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>498786728.2</t>
+          <t>487945910.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>463094155.0</t>
+          <t>469310663.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3237534067.52</t>
+          <t>3055293723.54</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>35692573</t>
+          <t>18635247</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-283449258.4345579</t>
+          <t>-262615306.766223</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-163047340.02</v>
+        <v>-148028572.59</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11439.749</t>
+          <t>10271.075</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-26.37</t>
+          <t>-25.48</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,72 +5319,72 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-12.86</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>12.22</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>50.72000000000001</t>
+          <t>50.52</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>52.84</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60.82</t>
+          <t>60.63</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>53.86</t>
+          <t>54.03</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-135.87</t>
+          <t>-135.86</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1140767747.87013</t>
+          <t>1140487994.401297</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>575830981.0</t>
+          <t>511653304.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>491046483.6</t>
+          <t>498786728.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>466191474.3</t>
+          <t>463094155.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3329174084.28</t>
+          <t>3237534067.52</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>24855009</t>
+          <t>35692573</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-305340516.3289255</t>
+          <t>-283449258.4345579</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-183733037.19</v>
+        <v>-163047340.02</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1199384865.4</t>
+          <t>751503060.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1647059956.98</t>
+          <t>1565117969.24</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>17580088.43</v>
+        <v>-13116137.58</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1149525583.8</t>
+          <t>1199384865.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1776903570.96</t>
+          <t>1647059956.98</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>44201426.71</v>
+        <v>17580088.43</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,67 +1871,67 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>57.56</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1030169557.8</t>
+          <t>1149525583.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1957468999.34</t>
+          <t>1776903570.96</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>50764557.16</v>
+        <v>44201426.71</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>61794246.37</v>
+        <v>50764557.16</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.57</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>76961261.38</v>
+        <v>61794246.37</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-102649650.64</v>
+        <v>76961261.38</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
+          <t>-184380592.2611023</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-105526151.13</v>
+        <v>-102649650.64</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9726.752</t>
+          <t>6580.167</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.37</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-14.3</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>59.59</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-136.15</t>
+          <t>-136.69</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>458810419.0</t>
+          <t>313260581.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>583628887.2</t>
+          <t>531114807.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>529295603.5</t>
+          <t>511080645.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2895834496.86</t>
+          <t>2772797348.26</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>54333283</t>
+          <t>20034161</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-216279783.8905731</t>
+          <t>-199240763.4657515</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-98524978.08</v>
+        <v>-105526151.13</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18985.299</t>
+          <t>9726.752</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>-14.3</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>51.78</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>54.43</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-135.73</t>
+          <t>-136.15</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>907361816.0</t>
+          <t>458810419.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>595612832.4</t>
+          <t>583628887.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>525692219.6</t>
+          <t>529295603.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2953848981.62</t>
+          <t>2895834496.86</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>69920612</t>
+          <t>54333283</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-237689748.5834216</t>
+          <t>-216279783.8905731</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-100599178.58</v>
+        <v>-98524978.08</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>47.3</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>47.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9234.129</t>
+          <t>18985.299</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,17 +4888,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.94</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>49.98</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>51.78</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.42</t>
+          <t>60.17</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>54.19</t>
+          <t>54.31</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-135.56</t>
+          <t>-135.73</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>464487916.0</t>
+          <t>907361816.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>487945910.2</t>
+          <t>595612832.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>469310663.0</t>
+          <t>525692219.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>3055293723.54</t>
+          <t>2953848981.62</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>18635247</t>
+          <t>69920612</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-262615306.766223</t>
+          <t>-237689748.5834216</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-148028572.59</v>
+        <v>-100599178.58</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>26.43</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10271.075</t>
+          <t>9234.129</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-25.48</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-12.86</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.58</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>52.26</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60.63</t>
+          <t>60.42</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>54.03</t>
+          <t>54.19</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-135.86</t>
+          <t>-135.56</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1140487994.401297</t>
+          <t>1139874606.064748</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>511653304.0</t>
+          <t>464487916.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>498786728.2</t>
+          <t>487945910.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>463094155.0</t>
+          <t>469310663.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3237534067.52</t>
+          <t>3055293723.54</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>35692573</t>
+          <t>18635247</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-283449258.4345579</t>
+          <t>-262615306.766223</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-163047340.02</v>
+        <v>-148028572.59</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>26.43</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>56.17</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,175 +1104,175 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1139874606.064748</t>
+          <t>1139161611.599138</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>751503060.6</t>
+          <t>664802561.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1565117969.24</t>
+          <t>1482928219.1</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-13116137.58</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-46255477.6478352</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-37803224.47222078</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>429086972</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>19.20</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>6.93</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>39929</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1277,20 +1282,25 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>47.8</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1139874606.064748</t>
+          <t>1139161611.599138</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1199384865.4</t>
+          <t>751503060.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1647059956.98</t>
+          <t>1565117969.24</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>17580088.43</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-47792250.95249236</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-13116137.5801748</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>476122067</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>22.32</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>6.93</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>39929</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>49.2</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>48.7</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1139874606.064748</t>
+          <t>1139161611.599138</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1149525583.8</t>
+          <t>1199384865.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1776903570.96</t>
+          <t>1647059956.98</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>44201426.71</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-54096998.83836829</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>17580088.42918277</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>631079227</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>21.82</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>22.32</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>6.93</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>39929</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>49.05</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,67 +2322,67 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>57.56</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2372,7 +2392,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1139874606.064748</t>
+          <t>1139161611.599138</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1030169557.8</t>
+          <t>1149525583.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1957468999.34</t>
+          <t>1776903570.96</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>50764557.16</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-67129196.52337757</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>44201426.71293712</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>910040711</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>27.93</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>21.82</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>6.93</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>39929</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>51.0</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>48.85</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1139874606.064748</t>
+          <t>1139161611.599138</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>61794246.37</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-87371128.02088934</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>50764557.16426682</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>877683832</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>26.68</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>27.93</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>6.93</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>39929</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1139874606.064748</t>
+          <t>1139161611.599138</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>76961261.38</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-112486707.1454632</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>61794246.37458563</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>862589466</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>26.68</t>
         </is>
       </c>
-      <c r="BH7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>1.59</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>6.93</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>39929</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>50.8</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1139874606.064748</t>
+          <t>1139161611.599138</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-102649650.64</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-144174153.2400175</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>76961261.37594843</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>2715531091</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>28.93</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>26.68</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>6.93</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>39929</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
         <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>50.8</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1139874606.064748</t>
+          <t>1139161611.599138</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-105526151.13</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-184380592.2611023</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-102649650.6355312</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>381782819</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>17.21</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>28.93</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>6.93</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>39929</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>51.7</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9726.752</t>
+          <t>6580.167</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.37</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-14.3</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>59.59</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-136.15</t>
+          <t>-136.69</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1139874606.064748</t>
+          <t>1139161611.599138</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>458810419.0</t>
+          <t>313260581.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>583628887.2</t>
+          <t>531114807.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>529295603.5</t>
+          <t>511080645.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2895834496.86</t>
+          <t>2772797348.26</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>54333283</t>
+          <t>20034161</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-216279783.8905731</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-98524978.08</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-199240763.4657515</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-105526151.1292332</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>313260581</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>17.96</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>17.21</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價跌量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>6.93</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>39929</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18985.299</t>
+          <t>9726.752</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>-14.3</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>51.78</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>54.43</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-135.73</t>
+          <t>-136.15</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1139874606.064748</t>
+          <t>1139161611.599138</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>907361816.0</t>
+          <t>458810419.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>595612832.4</t>
+          <t>583628887.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>525692219.6</t>
+          <t>529295603.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2953848981.62</t>
+          <t>2895834496.86</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>69920612</t>
+          <t>54333283</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-237689748.5834216</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-100599178.58</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-216279783.8905731</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-98524978.07990623</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>458810419</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>18.45</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>17.96</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>6.93</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>39929</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>48.3</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>47.95</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>47.3</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9234.129</t>
+          <t>18985.299</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>13.30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>10.91</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,17 +5374,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.49</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-13.51</t>
+          <t>-13.94</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>10.79</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>50.58</t>
+          <t>49.98</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>52.26</t>
+          <t>51.78</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60.42</t>
+          <t>60.17</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>54.19</t>
+          <t>54.31</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-135.56</t>
+          <t>-135.73</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1139874606.064748</t>
+          <t>1139161611.599138</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>464487916.0</t>
+          <t>907361816.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>487945910.2</t>
+          <t>595612832.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>469310663.0</t>
+          <t>525692219.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3055293723.54</t>
+          <t>2953848981.62</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>18635247</t>
+          <t>69920612</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-262615306.766223</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-148028572.59</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-237689748.5834216</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-100599178.5780139</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>907361816</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>26.43</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>7.06</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>6.93</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>39929</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.77</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>56.17</t>
+          <t>55.78</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>664802561.8</t>
+          <t>549695262.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1482928219.1</t>
+          <t>1388106125.2</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>429086972</v>
+        <v>302147334</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>56.17</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>751503060.6</t>
+          <t>664802561.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1565117969.24</t>
+          <t>1482928219.1</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>476122067</v>
+        <v>429086972</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1199384865.4</t>
+          <t>751503060.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1647059956.98</t>
+          <t>1565117969.24</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>631079227</v>
+        <v>476122067</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1149525583.8</t>
+          <t>1199384865.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1776903570.96</t>
+          <t>1647059956.98</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>910040711</v>
+        <v>631079227</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,67 +2758,67 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>57.56</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1030169557.8</t>
+          <t>1149525583.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1957468999.34</t>
+          <t>1776903570.96</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>877683832</v>
+        <v>910040711</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-7.66</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>61794246.37458563</t>
+          <t>50764557.16426682</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>862589466</v>
+        <v>877683832</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>76961261.37594843</t>
+          <t>61794246.37458563</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>2715531091</v>
+        <v>862589466</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,17 +3888,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-6.61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-102649650.6355312</t>
+          <t>76961261.37594843</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>381782819</v>
+        <v>2715531091</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-8.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
+          <t>-184380592.2611023</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-105526151.1292332</t>
+          <t>-102649650.6355312</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>313260581</v>
+        <v>381782819</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,17 +4695,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9726.752</t>
+          <t>6580.167</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.37</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-14.3</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>59.59</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-136.15</t>
+          <t>-136.69</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>458810419.0</t>
+          <t>313260581.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>583628887.2</t>
+          <t>531114807.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>529295603.5</t>
+          <t>511080645.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2895834496.86</t>
+          <t>2772797348.26</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>54333283</t>
+          <t>20034161</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-216279783.8905731</t>
+          <t>-199240763.4657515</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-98524978.07990623</t>
+          <t>-105526151.1292332</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>458810419</v>
+        <v>313260581</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18985.299</t>
+          <t>9726.752</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-29.93</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.49</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-13.94</t>
+          <t>-14.3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>10.12</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>51.78</t>
+          <t>51.37</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>54.43</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-135.73</t>
+          <t>-136.15</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1139161611.599138</t>
+          <t>1138177478.728838</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>907361816.0</t>
+          <t>458810419.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>595612832.4</t>
+          <t>583628887.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>525692219.6</t>
+          <t>529295603.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2953848981.62</t>
+          <t>2895834496.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>69920612</t>
+          <t>54333283</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-237689748.5834216</t>
+          <t>-216279783.8905731</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-100599178.5780139</t>
+          <t>-98524978.07990623</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>907361816</v>
+        <v>458810419</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>47.3</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>47.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>49.77</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>55.78</t>
+          <t>55.39</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>549695262.2</t>
+          <t>427404646.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1388106125.2</t>
+          <t>1336844077.5</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>302147334</v>
+        <v>298587633</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.77</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>56.17</t>
+          <t>55.78</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>664802561.8</t>
+          <t>549695262.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1482928219.1</t>
+          <t>1388106125.2</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>429086972</v>
+        <v>302147334</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>56.17</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>751503060.6</t>
+          <t>664802561.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1565117969.24</t>
+          <t>1482928219.1</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>476122067</v>
+        <v>429086972</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1199384865.4</t>
+          <t>751503060.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1647059956.98</t>
+          <t>1565117969.24</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>631079227</v>
+        <v>476122067</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1149525583.8</t>
+          <t>1199384865.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1776903570.96</t>
+          <t>1647059956.98</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>910040711</v>
+        <v>631079227</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.66</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,67 +3194,67 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>57.56</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1030169557.8</t>
+          <t>1149525583.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1957468999.34</t>
+          <t>1776903570.96</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>877683832</v>
+        <v>910040711</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>-6.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>61794246.37458563</t>
+          <t>50764557.16426682</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>862589466</v>
+        <v>877683832</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.61</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>76961261.37594843</t>
+          <t>61794246.37458563</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>2715531091</v>
+        <v>862589466</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,17 +4324,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.5</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-102649650.6355312</t>
+          <t>76961261.37594843</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>381782819</v>
+        <v>2715531091</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,97 +4650,97 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>26.68</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>宏達電</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>宏達電</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>通信網路業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-36.86822403006653</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-14.58459224643812</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-2.04560003730758</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>7.01</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>35.20%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>-119.21%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
           <t>28.93</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>宏達電</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>宏達電</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>通信網路業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-36.86822403006653</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-14.58459224643812</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>-2.04560003730758</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>6.91</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>35.20%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>-119.21%</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>28.44</t>
-        </is>
-      </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-6.93</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
+          <t>-184380592.2611023</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-105526151.1292332</t>
+          <t>-102649650.6355312</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>313260581</v>
+        <v>381782819</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9726.752</t>
+          <t>6580.167</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.93</t>
+          <t>-30.37</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-14.3</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>50.99</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>59.59</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-136.15</t>
+          <t>-136.69</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1138177478.728838</t>
+          <t>1137188515.936246</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>458810419.0</t>
+          <t>313260581.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>583628887.2</t>
+          <t>531114807.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>529295603.5</t>
+          <t>511080645.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2895834496.86</t>
+          <t>2772797348.26</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>54333283</t>
+          <t>20034161</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-216279783.8905731</t>
+          <t>-199240763.4657515</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-98524978.07990623</t>
+          <t>-105526151.1292332</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>458810419</v>
+        <v>313260581</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.46</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>55.04</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>427404646.6</t>
+          <t>359053739.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1336844077.5</t>
+          <t>1233289107.3</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>298587633</v>
+        <v>289324693</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>49.77</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>55.78</t>
+          <t>55.39</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>549695262.2</t>
+          <t>427404646.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1388106125.2</t>
+          <t>1336844077.5</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>302147334</v>
+        <v>298587633</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.77</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>56.17</t>
+          <t>55.78</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>664802561.8</t>
+          <t>549695262.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1482928219.1</t>
+          <t>1388106125.2</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>429086972</v>
+        <v>302147334</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,102 +2216,102 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-17.48</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-01-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>41.8</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-29.19</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-13.01</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>5.15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>-0.72</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-11.94</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-07-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-01-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>48.05</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-27.85</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-13.01</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>5.54</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-3.08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>56.17</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>751503060.6</t>
+          <t>664802561.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1565117969.24</t>
+          <t>1482928219.1</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>476122067</v>
+        <v>429086972</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>50.18</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1199384865.4</t>
+          <t>751503060.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1647059956.98</t>
+          <t>1565117969.24</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>631079227</v>
+        <v>476122067</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>50.38</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1149525583.8</t>
+          <t>1199384865.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1776903570.96</t>
+          <t>1647059956.98</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>910040711</v>
+        <v>631079227</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,67 +3630,67 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>57.56</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1030169557.8</t>
+          <t>1149525583.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1957468999.34</t>
+          <t>1776903570.96</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>877683832</v>
+        <v>910040711</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3893,17 +3893,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>50.73</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.07</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>946394875.2</t>
+          <t>1030169557.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2163437979.1</t>
+          <t>1957468999.34</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>61794246.37458563</t>
+          <t>50764557.16426682</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>862589466</v>
+        <v>877683832</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>50.73</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>955349345.2</t>
+          <t>946394875.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2402549153.18</t>
+          <t>2163437979.1</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>76961261.37594843</t>
+          <t>61794246.37458563</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>2715531091</v>
+        <v>862589466</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.93</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>505140710.2</t>
+          <t>955349345.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2548936714.28</t>
+          <t>2402549153.18</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-102649650.6355312</t>
+          <t>76961261.37594843</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>381782819</v>
+        <v>2715531091</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6580.167</t>
+          <t>7426.262</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-5.3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-30.37</t>
+          <t>-23.41</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>48.84</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>50.99</t>
+          <t>50.98</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.59</t>
+          <t>59.29</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-136.69</t>
+          <t>-136.12</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1137188515.936246</t>
+          <t>1136182505.240343</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>313260581.0</t>
+          <t>381782819.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>531114807.2</t>
+          <t>505140710.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>511080645.4</t>
+          <t>501963719.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2772797348.26</t>
+          <t>2548936714.28</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>20034161</t>
+          <t>3176991</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-199240763.4657515</t>
+          <t>-184380592.2611023</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-105526151.1292332</t>
+          <t>-102649650.6355312</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>313260581</v>
+        <v>381782819</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>48.32</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>49.46</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>55.04</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>55.04</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>289324693.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>359053739.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>359053739.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>779219302.6</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1233289107.3</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1233289107.3</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-90860825.19125909</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>289324693</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>289324693.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>48.31</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>49.57</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>55.39</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>55.39</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>298587633.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>427404646.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>427404646.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>788465115.2</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1336844077.5</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1336844077.5</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-80434512.81531477</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>298587633</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>298587633.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>48.41</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>49.77</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>55.78</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>55.78</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>302147334.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>549695262.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>549695262.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>789932410.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1388106125.2</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1388106125.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-63659577.53484738</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>302147334</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>302147334.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>49.14</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>56.17</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>56.17</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>429086972.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>664802561.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>664802561.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>805598718.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1482928219.1</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1482928219.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-37803224.47222078</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>429086972</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>429086972.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>49.73999999999999</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>50.18</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>56.62</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>56.62</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>476122067.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>751503060.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>751503060.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>853426202.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1565117969.24</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1565117969.24</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-13116137.5801748</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>476122067</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>476122067.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>50.16</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>50.38</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>57.1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>631079227.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>1199384865.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>1199384865.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>852262787.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1647059956.98</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1647059956.98</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>17580088.42918277</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>631079227</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>631079227.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>50.69</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>50.56</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>57.56</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>50.56</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>57.56</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>910040711.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1149525583.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1149525583.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>840320195.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1776903570.96</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1776903570.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>44201426.71293712</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>910040711</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>910040711.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>50.32</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>50.72</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>58.07</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>58.07</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>877683832.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1030169557.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1030169557.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>806899222.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1957468999.34</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1957468999.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>50764557.16426682</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>877683832</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>877683832.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>49.52</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>50.73</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>58.46</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>862589466.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>946394875.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>946394875.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>771003853.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2163437979.1</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>2163437979.1</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>61794246.37458563</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>862589466</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>862589466.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>48.86</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>50.84</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>58.9</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>2715531091.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>955349345.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>955349345.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>721647627.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>2402549153.18</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>2402549153.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>76961261.37594843</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>2715531091</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2715531091.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>48.84</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>50.98</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>59.29</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>50.98</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>59.29</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>381782819.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>505140710.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>505140710.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>501963719.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>2548936714.28</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>2548936714.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-102649650.6355312</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>381782819</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>381782819.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN3" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN4" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN5" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>50.18</v>
+        <v>50</v>
       </c>
       <c r="AN6" t="n">
-        <v>56.62</v>
+        <v>56.17</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>751503060.6</v>
+        <v>664802561.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1565117969.24</v>
+        <v>1482928219.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>50.38</v>
+        <v>50.18</v>
       </c>
       <c r="AN7" t="n">
-        <v>57.1</v>
+        <v>56.62</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1199384865.4</v>
+        <v>751503060.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1647059956.98</v>
+        <v>1565117969.24</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>50.56</v>
+        <v>50.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>57.56</v>
+        <v>57.1</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1149525583.8</v>
+        <v>1199384865.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1776903570.96</v>
+        <v>1647059956.98</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,63 +4024,63 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>50.72</v>
+        <v>50.56</v>
       </c>
       <c r="AN9" t="n">
-        <v>58.07</v>
+        <v>57.56</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1030169557.8</v>
+        <v>1149525583.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1957468999.34</v>
+        <v>1776903570.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>50.73</v>
+        <v>50.72</v>
       </c>
       <c r="AN10" t="n">
-        <v>58.46</v>
+        <v>58.07</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>946394875.2</v>
+        <v>1030169557.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2163437979.1</v>
+        <v>1957468999.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>61794246.37458563</t>
+          <t>50764557.16426682</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>50.84</v>
+        <v>50.73</v>
       </c>
       <c r="AN11" t="n">
-        <v>58.9</v>
+        <v>58.46</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>955349345.2</v>
+        <v>946394875.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2402549153.18</v>
+        <v>2163437979.1</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>76961261.37594843</t>
+          <t>61794246.37458563</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,17 +5136,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7426.262</t>
+          <t>52365.835</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.3</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.41</t>
+          <t>-24.74</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-14.03</t>
+          <t>-13.69</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>48.86</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>50.98</v>
+        <v>50.84</v>
       </c>
       <c r="AN12" t="n">
-        <v>59.29</v>
+        <v>58.9</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-136.12</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1136182505.240343</t>
+          <t>1135002713.732143</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>505140710.2</v>
+        <v>955349345.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>501963719.2</t>
+          <t>721647627.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2548936714.28</v>
+        <v>2402549153.18</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3176991</t>
+          <t>233701717</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-184380592.2611023</t>
+          <t>-144174153.2400175</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-102649650.6355312</t>
+          <t>76961261.37594843</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>381782819.0</t>
+          <t>2715531091.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>29.44</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>50.3</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6085.789</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4211.204</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN2" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN4" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN5" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN6" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>50.18</v>
+        <v>50</v>
       </c>
       <c r="AN7" t="n">
-        <v>56.62</v>
+        <v>56.17</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>751503060.6</v>
+        <v>664802561.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1565117969.24</v>
+        <v>1482928219.1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>50.38</v>
+        <v>50.18</v>
       </c>
       <c r="AN8" t="n">
-        <v>57.1</v>
+        <v>56.62</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1199384865.4</v>
+        <v>751503060.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1647059956.98</v>
+        <v>1565117969.24</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>50.56</v>
+        <v>50.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>57.56</v>
+        <v>57.1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1149525583.8</v>
+        <v>1199384865.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1776903570.96</v>
+        <v>1647059956.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,63 +4454,63 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>50.72</v>
+        <v>50.56</v>
       </c>
       <c r="AN10" t="n">
-        <v>58.07</v>
+        <v>57.56</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1030169557.8</v>
+        <v>1149525583.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1957468999.34</v>
+        <v>1776903570.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>50.73</v>
+        <v>50.72</v>
       </c>
       <c r="AN11" t="n">
-        <v>58.46</v>
+        <v>58.07</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>946394875.2</v>
+        <v>1030169557.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2163437979.1</v>
+        <v>1957468999.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>61794246.37458563</t>
+          <t>50764557.16426682</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>52365.835</t>
+          <t>16854.118</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-13.22</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>48.86</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>50.84</v>
+        <v>50.73</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.9</v>
+        <v>58.46</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>54.85</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>17.41</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-133.56</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1135002713.732143</t>
+          <t>1134029839.354494</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>955349345.2</v>
+        <v>946394875.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>721647627.7</t>
+          <t>771003853.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2402549153.18</v>
+        <v>2163437979.1</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>233701717</t>
+          <t>175391021</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-144174153.2400175</t>
+          <t>-112486707.1454632</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>76961261.37594843</t>
+          <t>61794246.37458563</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2715531091.0</t>
+          <t>862589466.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41725</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AN2" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>48.95</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>49.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4211.204</t>
+          <t>6085.789</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN3" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN5" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN6" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN7" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>50.18</v>
+        <v>50</v>
       </c>
       <c r="AN8" t="n">
-        <v>56.62</v>
+        <v>56.17</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>751503060.6</v>
+        <v>664802561.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1565117969.24</v>
+        <v>1482928219.1</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>50.38</v>
+        <v>50.18</v>
       </c>
       <c r="AN9" t="n">
-        <v>57.1</v>
+        <v>56.62</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1199384865.4</v>
+        <v>751503060.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1647059956.98</v>
+        <v>1565117969.24</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>50.56</v>
+        <v>50.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>57.56</v>
+        <v>57.1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1149525583.8</v>
+        <v>1199384865.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1776903570.96</v>
+        <v>1647059956.98</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,63 +4884,63 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>50.72</v>
+        <v>50.56</v>
       </c>
       <c r="AN11" t="n">
-        <v>58.07</v>
+        <v>57.56</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1030169557.8</v>
+        <v>1149525583.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1957468999.34</v>
+        <v>1776903570.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16854.118</t>
+          <t>16934.062</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-24.74</t>
+          <t>-24.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-12.67</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>50.32</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>50.73</v>
+        <v>50.72</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.46</v>
+        <v>58.07</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>54.85</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>17.41</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-133.56</t>
+          <t>-131.76</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1134029839.354494</t>
+          <t>1133097683.061966</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>946394875.2</v>
+        <v>1030169557.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>771003853.8</t>
+          <t>806899222.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2163437979.1</v>
+        <v>1957468999.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>175391021</t>
+          <t>223270335</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-112486707.1454632</t>
+          <t>-87371128.02088934</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>61794246.37458563</t>
+          <t>50764557.16426682</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>862589466.0</t>
+          <t>877683832.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>64.49</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.23</v>
+        <v>49.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>54.08</v>
+        <v>53.68</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-121.89</t>
+          <t>-120.81</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>283316111.4</v>
+        <v>267060943</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>416505686.8</t>
+          <t>347232794.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1087982910.56</v>
+        <v>1007913686.44</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-133189575</t>
+          <t>-80171851</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-74959775.3529597</t>
+          <t>-78323679.09920117</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-95106052.24594092</t>
+          <t>-96825149.70352924</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AN3" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>48.95</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>49.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4211.204</t>
+          <t>6085.789</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN4" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN5" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN6" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN7" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN8" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>50.18</v>
+        <v>50</v>
       </c>
       <c r="AN9" t="n">
-        <v>56.62</v>
+        <v>56.17</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>751503060.6</v>
+        <v>664802561.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1565117969.24</v>
+        <v>1482928219.1</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>50.38</v>
+        <v>50.18</v>
       </c>
       <c r="AN10" t="n">
-        <v>57.1</v>
+        <v>56.62</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1199384865.4</v>
+        <v>751503060.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1647059956.98</v>
+        <v>1565117969.24</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>36.80</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-27.63</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>50.56</v>
+        <v>50.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>57.56</v>
+        <v>57.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1149525583.8</v>
+        <v>1199384865.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1776903570.96</v>
+        <v>1647059956.98</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16934.062</t>
+          <t>18405.677</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>36.80</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-24.00</t>
+          <t>-27.63</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,63 +5314,63 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-12.67</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>50.69</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>50.72</v>
+        <v>50.56</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.07</v>
+        <v>57.56</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.11</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-131.76</t>
+          <t>-130.33</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1133097683.061966</t>
+          <t>1131949560.733997</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1030169557.8</v>
+        <v>1149525583.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>806899222.5</t>
+          <t>840320195.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1957468999.34</v>
+        <v>1776903570.96</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>223270335</t>
+          <t>309205388</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-87371128.02088934</t>
+          <t>-67129196.52337757</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>50764557.16426682</t>
+          <t>44201426.71293712</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>877683832.0</t>
+          <t>910040711.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>21.82</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4440.277</t>
+          <t>5508.131</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-23.09</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-27.04</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>64.49</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.17</v>
+        <v>49.12</v>
       </c>
       <c r="AN2" t="n">
-        <v>53.68</v>
+        <v>53.27</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.81</t>
+          <t>-119.67</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>267060943</v>
+        <v>263666319.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>347232794.8</t>
+          <t>311360029.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1007913686.44</v>
+        <v>893391430.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-80171851</t>
+          <t>-47693710</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-78323679.09920117</t>
+          <t>-80347713.91182451</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-96825149.70352924</t>
+          <t>-91479905.38125283</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>64.49</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.23</v>
+        <v>49.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>54.08</v>
+        <v>53.68</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-121.89</t>
+          <t>-120.81</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>283316111.4</v>
+        <v>267060943</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>416505686.8</t>
+          <t>347232794.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1087982910.56</v>
+        <v>1007913686.44</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-133189575</t>
+          <t>-80171851</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-74959775.3529597</t>
+          <t>-78323679.09920117</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-95106052.24594092</t>
+          <t>-96825149.70352924</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AN4" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>48.95</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>49.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,42 +2173,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6085.789</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4211.204</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-1.24</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN5" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN6" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN7" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN8" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN9" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>50.18</v>
+        <v>50</v>
       </c>
       <c r="AN10" t="n">
-        <v>56.62</v>
+        <v>56.17</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>751503060.6</v>
+        <v>664802561.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1565117969.24</v>
+        <v>1482928219.1</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>50.38</v>
+        <v>50.18</v>
       </c>
       <c r="AN11" t="n">
-        <v>57.1</v>
+        <v>56.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1199384865.4</v>
+        <v>751503060.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1647059956.98</v>
+        <v>1565117969.24</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18405.677</t>
+          <t>12834.389</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,102 +5208,102 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>40.73</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-01-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>41.8</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-27.33</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>-13.01</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>-0.78</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>36.80</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-07-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-01-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>48.05</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-27.63</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>-13.01</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10.58</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>-2.73</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>58.16</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.78</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>50.56</v>
+        <v>50.38</v>
       </c>
       <c r="AN12" t="n">
-        <v>57.56</v>
+        <v>57.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-130.33</t>
+          <t>-129.08</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1131949560.733997</t>
+          <t>1130921972.384233</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1149525583.8</v>
+        <v>1199384865.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>840320195.5</t>
+          <t>852262787.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1776903570.96</v>
+        <v>1647059956.98</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>309205388</t>
+          <t>347122077</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-67129196.52337757</t>
+          <t>-54096998.83836829</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>44201426.71293712</t>
+          <t>17580088.42918277</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>910040711.0</t>
+          <t>631079227.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.91</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5508.131</t>
+          <t>8142.579</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.04</t>
+          <t>-27.11</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.12</v>
+        <v>49.04</v>
       </c>
       <c r="AN2" t="n">
-        <v>53.27</v>
+        <v>52.89</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-119.67</t>
+          <t>-118.51</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>263666319.4</v>
+        <v>303258012.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>311360029.6</t>
+          <t>304232232.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>893391430.4</v>
+        <v>833966853.42</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-47693710</t>
+          <t>-974220</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-80347713.91182451</t>
+          <t>-79604111.38633272</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-91479905.38125283</t>
+          <t>-75514297.49612796</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4440.277</t>
+          <t>5508.131</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-23.09</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-27.04</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>64.49</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.17</v>
+        <v>49.12</v>
       </c>
       <c r="AN3" t="n">
-        <v>53.68</v>
+        <v>53.27</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.81</t>
+          <t>-119.67</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>267060943</v>
+        <v>263666319.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>347232794.8</t>
+          <t>311360029.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1007913686.44</v>
+        <v>893391430.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-80171851</t>
+          <t>-47693710</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-78323679.09920117</t>
+          <t>-80347713.91182451</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-96825149.70352924</t>
+          <t>-91479905.38125283</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>64.49</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.23</v>
+        <v>49.17</v>
       </c>
       <c r="AN4" t="n">
-        <v>54.08</v>
+        <v>53.68</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-121.89</t>
+          <t>-120.81</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>283316111.4</v>
+        <v>267060943</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>416505686.8</t>
+          <t>347232794.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1087982910.56</v>
+        <v>1007913686.44</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-133189575</t>
+          <t>-80171851</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-74959775.3529597</t>
+          <t>-78323679.09920117</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-95106052.24594092</t>
+          <t>-96825149.70352924</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AN5" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>48.95</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>49.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,42 +2603,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6085.789</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.52</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>4211.204</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN6" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN7" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN8" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN9" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN10" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>32.27</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>50.18</v>
+        <v>50</v>
       </c>
       <c r="AN11" t="n">
-        <v>56.62</v>
+        <v>56.17</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>751503060.6</v>
+        <v>664802561.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1565117969.24</v>
+        <v>1482928219.1</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12834.389</t>
+          <t>9634.482</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>-11.94</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-27.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>58.16</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.78</t>
+          <t>-11.37</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>50.38</v>
+        <v>50.18</v>
       </c>
       <c r="AN12" t="n">
-        <v>57.1</v>
+        <v>56.62</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-129.08</t>
+          <t>-128.03</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1130921972.384233</t>
+          <t>1130179198.16383</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1199384865.4</v>
+        <v>751503060.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>852262787.8</t>
+          <t>853426202.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1647059956.98</v>
+        <v>1565117969.24</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>347122077</t>
+          <t>-101923142</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-54096998.83836829</t>
+          <t>-47792250.95249236</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>17580088.42918277</t>
+          <t>-13116137.5801748</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>631079227.0</t>
+          <t>476122067.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>29.84</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】;【x】看好</t>
+          <t>【d1】;【d2】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8142.579</t>
+          <t>11750.074</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.11</t>
+          <t>-25.33</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,74 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>57.97</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
+          <t>78.99</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.15</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.04</v>
+        <v>49.19</v>
       </c>
       <c r="AN2" t="n">
-        <v>52.89</v>
+        <v>52.61</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>25.08</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-1.30</t>
-        </is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-1.2</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-118.51</t>
+          <t>-117.08</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1130179198.16383</t>
+          <t>1129834534.37677</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>303258012.4</v>
+        <v>361101851</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>304232232.7</t>
+          <t>320446639.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>833966853.42</v>
+        <v>788698875.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-974220</t>
+          <t>40655211</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-79604111.38633272</t>
+          <t>-74814477.89061035</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-75514297.49612796</t>
+          <t>-48471493.66413736</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5508.131</t>
+          <t>8142.579</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1350,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-27.04</t>
+          <t>-27.11</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,74 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>54.35</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
+          <t>57.97</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.26</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.12</v>
+        <v>49.04</v>
       </c>
       <c r="AN3" t="n">
-        <v>53.27</v>
+        <v>52.89</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>23.29</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-1.38</t>
-        </is>
+          <t>25.08</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-1.3</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-119.67</t>
+          <t>-118.51</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1130179198.16383</t>
+          <t>1129834534.37677</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>263666319.4</v>
+        <v>303258012.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>311360029.6</t>
+          <t>304232232.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>893391430.4</v>
+        <v>833966853.42</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-47693710</t>
+          <t>-974220</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-80347713.91182451</t>
+          <t>-79604111.38633272</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-91479905.38125283</t>
+          <t>-75514297.49612796</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4440.277</t>
+          <t>5508.131</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-23.09</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1772,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-27.04</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,74 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>64.49</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-1.26</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
+          <t>54.35</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.17</v>
+        <v>49.12</v>
       </c>
       <c r="AN4" t="n">
-        <v>53.68</v>
+        <v>53.27</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>20.72</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-1.16</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-1.46</t>
-        </is>
+          <t>23.29</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-1.38</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.81</t>
+          <t>-119.67</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1130179198.16383</t>
+          <t>1129834534.37677</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>267060943</v>
+        <v>263666319.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>347232794.8</t>
+          <t>311360029.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1007913686.44</v>
+        <v>893391430.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-80171851</t>
+          <t>-47693710</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-78323679.09920117</t>
+          <t>-80347713.91182451</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-96825149.70352924</t>
+          <t>-91479905.38125283</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2047,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2161,11 +2137,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>2498</t>
@@ -2173,12 +2145,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2160,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2170,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2180,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2190,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2245,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2255,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2276,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>65.42</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
+          <t>64.49</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.23</v>
+        <v>49.17</v>
       </c>
       <c r="AN5" t="n">
-        <v>54.08</v>
+        <v>53.68</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>22.44</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-1.19</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-1.54</t>
-        </is>
+          <t>20.72</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-1.46</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2344,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-121.89</t>
+          <t>-120.81</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2354,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1130179198.16383</t>
+          <t>1129834534.37677</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>283316111.4</v>
+        <v>267060943</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>416505686.8</t>
+          <t>347232794.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1087982910.56</v>
+        <v>1007913686.44</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-133189575</t>
+          <t>-80171851</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-74959775.3529597</t>
+          <t>-78323679.09920117</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-95106052.24594092</t>
+          <t>-96825149.70352924</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2410,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2501,7 +2465,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2480,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2495,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2520,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2591,11 +2555,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>2498</t>
@@ -2603,12 +2563,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2578,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2588,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2598,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2608,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2663,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2673,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2694,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>59.82</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-1.09</t>
-        </is>
+          <t>65.42</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.28</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>22.18</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-1.63</t>
-        </is>
+          <t>22.44</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-1.54</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2762,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2772,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1130179198.16383</t>
+          <t>1129834534.37677</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2828,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2873,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2883,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2898,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2913,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2938,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>48.95</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>49.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3021,11 +2973,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>2498</t>
@@ -3033,42 +2981,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6085.789</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>4211.204</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3026,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3081,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3091,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3112,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>32.88</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-2.01</t>
-        </is>
+          <t>59.82</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-1.09</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN7" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>16.10</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-1.44</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-1.72</t>
-        </is>
+          <t>22.18</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-1.63</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3180,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3190,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1130179198.16383</t>
+          <t>1129834534.37677</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3246,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3361,7 +3301,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3316,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3331,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3356,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3451,11 +3391,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>2498</t>
@@ -3463,12 +3399,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,7 +3424,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3434,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3444,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3573,17 +3509,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3530,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,59 +3545,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>19.63</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-2.30</t>
-        </is>
+          <t>32.88</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-2.01</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN8" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>12.90</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-1.56</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-1.79</t>
-        </is>
+          <t>16.10</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-1.72</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3598,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3608,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1130179198.16383</t>
+          <t>1129834534.37677</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3806,7 +3734,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3749,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,17 +3774,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3881,11 +3809,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>2498</t>
@@ -3893,12 +3817,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3832,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3842,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3852,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3862,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3917,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3927,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3948,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>12.07</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-2.54</t>
-        </is>
+          <t>19.63</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-2.3</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN9" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>8.87</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-1.68</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
+          <t>12.90</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-1.79</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4016,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4026,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1130179198.16383</t>
+          <t>1129834534.37677</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4082,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4127,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4137,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4152,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4167,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4192,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4311,11 +4227,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>2498</t>
@@ -4323,12 +4235,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4250,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4260,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4270,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4280,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4335,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4345,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4366,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>17.73</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-2.73</t>
-        </is>
+          <t>12.07</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-2.54</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN10" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.76</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-1.74</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
+          <t>8.87</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-1.84</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4434,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4444,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1130179198.16383</t>
+          <t>1129834534.37677</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4500,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4545,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4555,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4570,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4585,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4610,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4741,11 +4645,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>2498</t>
@@ -4753,12 +4653,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4668,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4678,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4688,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4698,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4753,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4763,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4784,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>32.27</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-2.73</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
+          <t>17.73</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-2.73</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN11" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>10.69</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-1.72</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-1.92</t>
-        </is>
+          <t>7.76</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-1.88</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4852,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4862,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1130179198.16383</t>
+          <t>1129834534.37677</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4918,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4963,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5096,7 +4988,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5003,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5028,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5171,11 +5063,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>2498</t>
@@ -5183,12 +5071,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9634.482</t>
+          <t>8966.946</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5086,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5096,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5106,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.94</t>
+          <t>-17.48</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5116,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5171,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-27.85</t>
+          <t>-29.19</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5181,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,74 +5202,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>36.17</t>
+          <t>17.02</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>39.72</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
+          <t>32.27</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1.71</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>50.18</v>
+        <v>50</v>
       </c>
       <c r="AN12" t="n">
-        <v>56.62</v>
+        <v>56.17</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>55.43</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-1.68</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-1.97</t>
-        </is>
+          <t>10.69</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-1.92</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5270,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-128.03</t>
+          <t>-127.30</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5280,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1130179198.16383</t>
+          <t>1129834534.37677</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>751503060.6</v>
+        <v>664802561.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>853426202.9</t>
+          <t>805598718.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1565117969.24</v>
+        <v>1482928219.1</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-101923142</t>
+          <t>-140796156</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-47792250.95249236</t>
+          <t>-46255477.6478352</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-13116137.5801748</t>
+          <t>-37803224.47222078</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>476122067.0</t>
+          <t>429086972.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5336,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5381,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5391,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5406,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5421,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5446,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】;【d2】;【x】看好</t>
+          <t>【d1】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11750.074</t>
+          <t>20739.776</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.33</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,51 +1029,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>2.31</v>
+        <v>3.64</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.15</v>
+        <v>0.78</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.79000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.19</v>
+        <v>49.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>52.61</v>
+        <v>52.35</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.8</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.2</v>
+        <v>-1.07</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.08</t>
+          <t>-115.26</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1129834534.37677</t>
+          <t>1130487283.947666</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1060885654.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>361101851</v>
+        <v>509324832.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>320446639.8</t>
+          <t>396320471.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>788698875.08</v>
+        <v>782128914.8200001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>40655211</t>
+          <t>113004360</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-74814477.89061035</t>
+          <t>-62243888.64823037</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-48471493.66413736</t>
+          <t>6894352.184859514</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1060885654.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8142.579</t>
+          <t>11750.074</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-27.11</t>
+          <t>-25.33</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.06</v>
+        <v>2.31</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.04</v>
+        <v>49.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>52.89</v>
+        <v>52.61</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.98</v>
+        <v>-0.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-118.51</t>
+          <t>-117.08</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1129834534.37677</t>
+          <t>1130487283.947666</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>303258012.4</v>
+        <v>361101851</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>304232232.7</t>
+          <t>320446639.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>833966853.42</v>
+        <v>788698875.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-974220</t>
+          <t>40655211</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-79604111.38633272</t>
+          <t>-74814477.89061035</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-75514297.49612796</t>
+          <t>-48471493.66413736</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5508.131</t>
+          <t>8142.579</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-27.04</t>
+          <t>-27.11</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.12</v>
+        <v>49.04</v>
       </c>
       <c r="AN4" t="n">
-        <v>53.27</v>
+        <v>52.89</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.06</v>
+        <v>-0.98</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.38</v>
+        <v>-1.3</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-119.67</t>
+          <t>-118.51</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1129834534.37677</t>
+          <t>1130487283.947666</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>263666319.4</v>
+        <v>303258012.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>311360029.6</t>
+          <t>304232232.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>893391430.4</v>
+        <v>833966853.42</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-47693710</t>
+          <t>-974220</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-80347713.91182451</t>
+          <t>-79604111.38633272</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-91479905.38125283</t>
+          <t>-75514297.49612796</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2137,7 +2137,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2498</t>
@@ -2145,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4440.277</t>
+          <t>5508.131</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2160,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2170,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2180,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-23.09</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2245,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-27.04</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2255,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2276,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>64.49</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-1.26</v>
+        <v>0.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.17</v>
+        <v>49.12</v>
       </c>
       <c r="AN5" t="n">
-        <v>53.68</v>
+        <v>53.27</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.16</v>
+        <v>-1.06</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.46</v>
+        <v>-1.38</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2344,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.81</t>
+          <t>-119.67</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2354,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1129834534.37677</t>
+          <t>1130487283.947666</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>267060943</v>
+        <v>263666319.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>347232794.8</t>
+          <t>311360029.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1007913686.44</v>
+        <v>893391430.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-80171851</t>
+          <t>-47693710</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-78323679.09920117</t>
+          <t>-80347713.91182451</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-96825149.70352924</t>
+          <t>-91479905.38125283</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2410,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2455,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2465,7 +2469,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2480,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2495,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2520,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2555,7 +2559,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2498</t>
@@ -2563,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2578,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2588,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2598,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2663,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2673,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2694,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>64.49</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.29</v>
+        <v>-1.26</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.28</v>
+        <v>-0.1</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.23</v>
+        <v>49.17</v>
       </c>
       <c r="AN6" t="n">
-        <v>54.08</v>
+        <v>53.68</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.19</v>
+        <v>-1.16</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.54</v>
+        <v>-1.46</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2762,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-121.89</t>
+          <t>-120.81</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2772,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1129834534.37677</t>
+          <t>1130487283.947666</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>283316111.4</v>
+        <v>267060943</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>416505686.8</t>
+          <t>347232794.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1087982910.56</v>
+        <v>1007913686.44</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-133189575</t>
+          <t>-80171851</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-74959775.3529597</t>
+          <t>-78323679.09920117</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-95106052.24594092</t>
+          <t>-96825149.70352924</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2828,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2883,7 +2891,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2898,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2913,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2938,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2973,7 +2981,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2498</t>
@@ -2981,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2996,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3006,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3016,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3081,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3091,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3112,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>2.29</v>
+        <v>-0.29</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.09</v>
+        <v>-0.28</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AN7" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.27</v>
+        <v>-1.19</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.63</v>
+        <v>-1.54</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3180,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3190,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1129834534.37677</t>
+          <t>1130487283.947666</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3246,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3291,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3301,7 +3313,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3316,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3331,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3356,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>48.95</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>49.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3391,7 +3403,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2498</t>
@@ -3399,42 +3415,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6085.789</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>4211.204</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3499,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3509,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3530,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.45</v>
+        <v>2.29</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.01</v>
+        <v>-1.09</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN8" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.44</v>
+        <v>-1.27</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.72</v>
+        <v>-1.63</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3598,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3608,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1129834534.37677</t>
+          <t>1130487283.947666</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3664,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3719,7 +3735,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3734,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3749,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3774,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3809,7 +3825,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2498</t>
@@ -3817,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3842,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3852,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3927,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3948,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3963,51 +3983,51 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>-2.3</v>
+        <v>-2.01</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.56</v>
+        <v>-1.44</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.79</v>
+        <v>-1.72</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4016,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4026,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1129834534.37677</t>
+          <t>1130487283.947666</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4152,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4167,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4192,17 +4212,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4227,7 +4247,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>2498</t>
@@ -4235,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4250,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4260,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4270,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4335,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4345,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4366,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.08</v>
+        <v>1.61</v>
       </c>
       <c r="AI10" t="n">
-        <v>-2.54</v>
+        <v>-2.3</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN10" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.68</v>
+        <v>-1.56</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.84</v>
+        <v>-1.79</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4434,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4444,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1129834534.37677</t>
+          <t>1130487283.947666</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4500,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4545,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4555,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4570,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4585,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4610,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4645,7 +4669,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>2498</t>
@@ -4653,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4668,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4678,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4688,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4753,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4763,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4784,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-1.57</v>
+        <v>0.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>-2.73</v>
+        <v>-2.54</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN11" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.74</v>
+        <v>-1.68</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.88</v>
+        <v>-1.84</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4852,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4862,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1129834534.37677</t>
+          <t>1130487283.947666</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4918,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4963,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4973,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -4988,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5003,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5028,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5063,7 +5091,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>2498</t>
@@ -5071,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8966.946</t>
+          <t>6337.117</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5086,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5096,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5106,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-17.48</t>
+          <t>-30.41</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5171,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.19</t>
+          <t>-29.41</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5181,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5202,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="AH12" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="AI12" t="n">
         <v>-2.73</v>
       </c>
-      <c r="AI12" t="n">
-        <v>-1.71</v>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-10.77</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>50</v>
+        <v>49.77</v>
       </c>
       <c r="AN12" t="n">
-        <v>56.17</v>
+        <v>55.78</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>55.43</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.72</v>
+        <v>-1.74</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.92</v>
+        <v>-1.88</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5270,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-127.30</t>
+          <t>-126.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5280,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1129834534.37677</t>
+          <t>1130487283.947666</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>664802561.8</v>
+        <v>549695262.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>805598718.5</t>
+          <t>789932410.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1482928219.1</v>
+        <v>1388106125.2</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-140796156</t>
+          <t>-240237147</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-46255477.6478352</t>
+          <t>-48933031.4766063</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-37803224.47222078</t>
+          <t>-63659577.53484738</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>429086972.0</t>
+          <t>302147334.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5336,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5381,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5406,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5421,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5446,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】;【x】看好</t>
+          <t>價_量;【d1】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20739.776</t>
+          <t>17888.375</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,51 +1029,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>3.64</v>
+        <v>2.68</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.78</v>
+        <v>1.63</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.79000000000001</t>
+          <t>50.45</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.4</v>
+        <v>49.64</v>
       </c>
       <c r="AN2" t="n">
-        <v>52.35</v>
+        <v>52.11</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>62.45</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.07</v>
+        <v>-0.93</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-115.26</t>
+          <t>-113.20</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1130487283.947666</t>
+          <t>1130859364.813559</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1060885654.0</t>
+          <t>929280358.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>509324832.2</v>
+        <v>651718545.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>396320471.8</t>
+          <t>459389744.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>782128914.8200001</v>
+        <v>772359077.74</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>113004360</t>
+          <t>192328801</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-62243888.64823037</t>
+          <t>-47189799.89088174</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>6894352.184859514</t>
+          <t>35607688.27453578</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1060885654.0</t>
+          <t>929280358.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>51.8</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>51.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11750.074</t>
+          <t>20739.776</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.33</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1451,51 +1451,51 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>2.31</v>
+        <v>3.64</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.15</v>
+        <v>0.78</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.79000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.19</v>
+        <v>49.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>52.61</v>
+        <v>52.35</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.8</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.2</v>
+        <v>-1.07</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.08</t>
+          <t>-115.26</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1130487283.947666</t>
+          <t>1130859364.813559</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1060885654.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>361101851</v>
+        <v>509324832.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>320446639.8</t>
+          <t>396320471.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>788698875.08</v>
+        <v>782128914.8200001</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>40655211</t>
+          <t>113004360</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-74814477.89061035</t>
+          <t>-62243888.64823037</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-48471493.66413736</t>
+          <t>6894352.184859514</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1060885654.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8142.579</t>
+          <t>11750.074</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-27.11</t>
+          <t>-25.33</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.06</v>
+        <v>2.31</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.04</v>
+        <v>49.19</v>
       </c>
       <c r="AN4" t="n">
-        <v>52.89</v>
+        <v>52.61</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.98</v>
+        <v>-0.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-118.51</t>
+          <t>-117.08</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1130487283.947666</t>
+          <t>1130859364.813559</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>303258012.4</v>
+        <v>361101851</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>304232232.7</t>
+          <t>320446639.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>833966853.42</v>
+        <v>788698875.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-974220</t>
+          <t>40655211</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-79604111.38633272</t>
+          <t>-74814477.89061035</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-75514297.49612796</t>
+          <t>-48471493.66413736</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5508.131</t>
+          <t>8142.579</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-27.04</t>
+          <t>-27.11</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.12</v>
+        <v>49.04</v>
       </c>
       <c r="AN5" t="n">
-        <v>53.27</v>
+        <v>52.89</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.06</v>
+        <v>-0.98</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.38</v>
+        <v>-1.3</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-119.67</t>
+          <t>-118.51</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1130487283.947666</t>
+          <t>1130859364.813559</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>263666319.4</v>
+        <v>303258012.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>311360029.6</t>
+          <t>304232232.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>893391430.4</v>
+        <v>833966853.42</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-47693710</t>
+          <t>-974220</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-80347713.91182451</t>
+          <t>-79604111.38633272</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-91479905.38125283</t>
+          <t>-75514297.49612796</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4440.277</t>
+          <t>5508.131</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-23.09</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-27.04</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>64.49</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-1.26</v>
+        <v>0.2</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.17</v>
+        <v>49.12</v>
       </c>
       <c r="AN6" t="n">
-        <v>53.68</v>
+        <v>53.27</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.16</v>
+        <v>-1.06</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.46</v>
+        <v>-1.38</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.81</t>
+          <t>-119.67</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1130487283.947666</t>
+          <t>1130859364.813559</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>267060943</v>
+        <v>263666319.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>347232794.8</t>
+          <t>311360029.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1007913686.44</v>
+        <v>893391430.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-80171851</t>
+          <t>-47693710</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-78323679.09920117</t>
+          <t>-80347713.91182451</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-96825149.70352924</t>
+          <t>-91479905.38125283</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>64.49</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.29</v>
+        <v>-1.26</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.28</v>
+        <v>-0.1</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>49.23</v>
+        <v>49.17</v>
       </c>
       <c r="AN7" t="n">
-        <v>54.08</v>
+        <v>53.68</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.19</v>
+        <v>-1.16</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.54</v>
+        <v>-1.46</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-121.89</t>
+          <t>-120.81</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1130487283.947666</t>
+          <t>1130859364.813559</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>283316111.4</v>
+        <v>267060943</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>416505686.8</t>
+          <t>347232794.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1087982910.56</v>
+        <v>1007913686.44</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-133189575</t>
+          <t>-80171851</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-74959775.3529597</t>
+          <t>-78323679.09920117</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-95106052.24594092</t>
+          <t>-96825149.70352924</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2.29</v>
+        <v>-0.29</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.09</v>
+        <v>-0.28</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AN8" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.27</v>
+        <v>-1.19</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.63</v>
+        <v>-1.54</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1130487283.947666</t>
+          <t>1130859364.813559</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>48.95</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>49.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,42 +3837,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6085.789</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>4211.204</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>4.84</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>2.29</v>
       </c>
       <c r="AI9" t="n">
-        <v>-2.01</v>
+        <v>-1.09</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN9" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.44</v>
+        <v>-1.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.72</v>
+        <v>-1.63</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1130487283.947666</t>
+          <t>1130859364.813559</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,12 +4390,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4405,51 +4405,51 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AI10" t="n">
-        <v>-2.3</v>
+        <v>-2.01</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN10" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.56</v>
+        <v>-1.44</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.79</v>
+        <v>-1.72</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1130487283.947666</t>
+          <t>1130859364.813559</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,17 +4634,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.08</v>
+        <v>1.61</v>
       </c>
       <c r="AI11" t="n">
-        <v>-2.54</v>
+        <v>-2.3</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN11" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.68</v>
+        <v>-1.56</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.84</v>
+        <v>-1.79</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1130487283.947666</t>
+          <t>1130859364.813559</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6337.117</t>
+          <t>6182.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-30.41</t>
+          <t>-45.79</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-29.41</t>
+          <t>-28.37</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>17.73</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.57</v>
+        <v>0.08</v>
       </c>
       <c r="AI12" t="n">
-        <v>-2.73</v>
+        <v>-2.54</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.77</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>49.77</v>
+        <v>49.57</v>
       </c>
       <c r="AN12" t="n">
-        <v>55.78</v>
+        <v>55.39</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>55.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.74</v>
+        <v>-1.68</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.88</v>
+        <v>-1.84</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-126.78</t>
+          <t>-126.20</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1130487283.947666</t>
+          <t>1130859364.813559</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>549695262.2</v>
+        <v>427404646.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>789932410.0</t>
+          <t>788465115.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1388106125.2</v>
+        <v>1336844077.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-240237147</t>
+          <t>-361060468</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-48933031.4766063</t>
+          <t>-53779413.22102299</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-63659577.53484738</t>
+          <t>-80434512.81531477</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>302147334.0</t>
+          <t>298587633.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>47.9</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>47.3</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17888.375</t>
+          <t>44624.702</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>60.39</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-24.59</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>44625</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>2.68</v>
+        <v>0.24</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.63</v>
+        <v>2.37</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>50.45</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.64</v>
+        <v>49.6</v>
       </c>
       <c r="AN2" t="n">
-        <v>52.11</v>
+        <v>51.91</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>56.72</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>62.45</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.35</v>
+        <v>-0.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.93</v>
+        <v>-0.79</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-113.20</t>
+          <t>-111.27</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1130859364.813559</t>
+          <t>1134242083.377292</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>929280358.0</t>
+          <t>2352804551.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>651718545.6</v>
+        <v>1067809140.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>459389744.3</t>
+          <t>665737730.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>772359077.74</v>
+        <v>775901935.04</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>192328801</t>
+          <t>402071410</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-47189799.89088174</t>
+          <t>-15071192.86067748</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>35607688.27453578</t>
+          <t>161581145.8054459</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>929280358.0</t>
+          <t>2352804551.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20739.776</t>
+          <t>17888.375</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>44625</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1451,51 +1451,51 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>3.64</v>
+        <v>2.68</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.78</v>
+        <v>1.63</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.79000000000001</t>
+          <t>50.45</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.4</v>
+        <v>49.64</v>
       </c>
       <c r="AN3" t="n">
-        <v>52.35</v>
+        <v>52.11</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>62.45</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.07</v>
+        <v>-0.93</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-115.26</t>
+          <t>-113.20</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1130859364.813559</t>
+          <t>1134242083.377292</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1060885654.0</t>
+          <t>929280358.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>509324832.2</v>
+        <v>651718545.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>396320471.8</t>
+          <t>459389744.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>782128914.8200001</v>
+        <v>772359077.74</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>113004360</t>
+          <t>192328801</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-62243888.64823037</t>
+          <t>-47189799.89088174</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>6894352.184859514</t>
+          <t>35607688.27453578</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1060885654.0</t>
+          <t>929280358.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>51.8</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>51.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11750.074</t>
+          <t>20739.776</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.33</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>44625</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1873,51 +1873,51 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>2.31</v>
+        <v>3.64</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.15</v>
+        <v>0.78</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.79000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.19</v>
+        <v>49.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>52.61</v>
+        <v>52.35</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.8</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.2</v>
+        <v>-1.07</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-117.08</t>
+          <t>-115.26</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1130859364.813559</t>
+          <t>1134242083.377292</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1060885654.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>361101851</v>
+        <v>509324832.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>320446639.8</t>
+          <t>396320471.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>788698875.08</v>
+        <v>782128914.8200001</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>40655211</t>
+          <t>113004360</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-74814477.89061035</t>
+          <t>-62243888.64823037</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-48471493.66413736</t>
+          <t>6894352.184859514</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1060885654.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8142.579</t>
+          <t>11750.074</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-27.11</t>
+          <t>-25.33</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>44625</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.06</v>
+        <v>2.31</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.04</v>
+        <v>49.19</v>
       </c>
       <c r="AN5" t="n">
-        <v>52.89</v>
+        <v>52.61</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.98</v>
+        <v>-0.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-118.51</t>
+          <t>-117.08</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1130859364.813559</t>
+          <t>1134242083.377292</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>303258012.4</v>
+        <v>361101851</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>304232232.7</t>
+          <t>320446639.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>833966853.42</v>
+        <v>788698875.08</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-974220</t>
+          <t>40655211</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-79604111.38633272</t>
+          <t>-74814477.89061035</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-75514297.49612796</t>
+          <t>-48471493.66413736</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5508.131</t>
+          <t>8142.579</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-27.04</t>
+          <t>-27.11</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>44625</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.12</v>
+        <v>49.04</v>
       </c>
       <c r="AN6" t="n">
-        <v>53.27</v>
+        <v>52.89</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.06</v>
+        <v>-0.98</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.38</v>
+        <v>-1.3</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-119.67</t>
+          <t>-118.51</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1130859364.813559</t>
+          <t>1134242083.377292</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>263666319.4</v>
+        <v>303258012.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>311360029.6</t>
+          <t>304232232.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>893391430.4</v>
+        <v>833966853.42</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-47693710</t>
+          <t>-974220</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-80347713.91182451</t>
+          <t>-79604111.38633272</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-91479905.38125283</t>
+          <t>-75514297.49612796</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4440.277</t>
+          <t>5508.131</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-23.09</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-27.04</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>44625</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>64.49</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-1.26</v>
+        <v>0.2</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>49.17</v>
+        <v>49.12</v>
       </c>
       <c r="AN7" t="n">
-        <v>53.68</v>
+        <v>53.27</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.16</v>
+        <v>-1.06</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.46</v>
+        <v>-1.38</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.81</t>
+          <t>-119.67</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1130859364.813559</t>
+          <t>1134242083.377292</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>267060943</v>
+        <v>263666319.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>347232794.8</t>
+          <t>311360029.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1007913686.44</v>
+        <v>893391430.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-80171851</t>
+          <t>-47693710</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-78323679.09920117</t>
+          <t>-80347713.91182451</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-96825149.70352924</t>
+          <t>-91479905.38125283</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>44625</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>64.49</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-0.29</v>
+        <v>-1.26</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.28</v>
+        <v>-0.1</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>49.23</v>
+        <v>49.17</v>
       </c>
       <c r="AN8" t="n">
-        <v>54.08</v>
+        <v>53.68</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.19</v>
+        <v>-1.16</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.54</v>
+        <v>-1.46</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-121.89</t>
+          <t>-120.81</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1130859364.813559</t>
+          <t>1134242083.377292</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>283316111.4</v>
+        <v>267060943</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>416505686.8</t>
+          <t>347232794.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1087982910.56</v>
+        <v>1007913686.44</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-133189575</t>
+          <t>-80171851</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-74959775.3529597</t>
+          <t>-78323679.09920117</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-95106052.24594092</t>
+          <t>-96825149.70352924</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>44625</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>2.29</v>
+        <v>-0.29</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.09</v>
+        <v>-0.28</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AN9" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.27</v>
+        <v>-1.19</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.63</v>
+        <v>-1.54</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1130859364.813559</t>
+          <t>1134242083.377292</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>48.95</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>49.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,42 +4259,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6085.789</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4211.204</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>5.21</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>44625</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.45</v>
+        <v>2.29</v>
       </c>
       <c r="AI10" t="n">
-        <v>-2.01</v>
+        <v>-1.09</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN10" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.44</v>
+        <v>-1.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.72</v>
+        <v>-1.63</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1130859364.813559</t>
+          <t>1134242083.377292</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,12 +4812,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>44625</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4827,51 +4827,51 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" t="n">
-        <v>-2.3</v>
+        <v>-2.01</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN11" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.56</v>
+        <v>-1.44</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.79</v>
+        <v>-1.72</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1130859364.813559</t>
+          <t>1134242083.377292</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,17 +5056,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6182.1</t>
+          <t>5896.567</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-45.79</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-28.37</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>44625</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.08</v>
+        <v>1.61</v>
       </c>
       <c r="AI12" t="n">
-        <v>-2.54</v>
+        <v>-2.3</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.51</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>48.32</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>49.57</v>
+        <v>49.46</v>
       </c>
       <c r="AN12" t="n">
-        <v>55.39</v>
+        <v>55.04</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.71</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>12.90</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.68</v>
+        <v>-1.56</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.84</v>
+        <v>-1.79</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-126.20</t>
+          <t>-125.39</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1130859364.813559</t>
+          <t>1134242083.377292</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>427404646.6</v>
+        <v>359053739.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>788465115.2</t>
+          <t>779219302.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1336844077.5</v>
+        <v>1233289107.3</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-361060468</t>
+          <t>-420165562</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-53779413.22102299</t>
+          <t>-59484245.83182855</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-80434512.81531477</t>
+          <t>-90860825.19125909</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>298587633.0</t>
+          <t>289324693.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.06</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>43271</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44624.702</t>
+          <t>24262.603</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>60.39</t>
+          <t>60.75</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.59</t>
+          <t>-22.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>44625</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1033,47 +1033,47 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.24</v>
+        <v>1.29</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.37</v>
+        <v>3.38</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>51.34</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.6</v>
+        <v>49.66</v>
       </c>
       <c r="AN2" t="n">
-        <v>51.91</v>
+        <v>51.76</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>56.78</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>87.16</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.25</v>
+        <v>-0.08</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.79</v>
+        <v>-0.65</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-111.27</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1134242083.377292</t>
+          <t>1135341687.642253</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2352804551.0</t>
+          <t>1276640741.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1067809140.8</v>
+        <v>1242168469.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>665737730.1</t>
+          <t>772713240.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>775901935.04</v>
+        <v>766248058.12</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>402071410</t>
+          <t>469455228</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-15071192.86067748</t>
+          <t>12633721.68434163</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>161581145.8054459</t>
+          <t>165010751.6819468</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2352804551.0</t>
+          <t>1276640741.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17888.375</t>
+          <t>44624.702</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>60.39</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-24.59</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>44625</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>2.68</v>
+        <v>0.24</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.63</v>
+        <v>2.37</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>50.45</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.64</v>
+        <v>49.6</v>
       </c>
       <c r="AN3" t="n">
-        <v>52.11</v>
+        <v>51.91</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>56.72</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>62.45</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.35</v>
+        <v>-0.25</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.93</v>
+        <v>-0.79</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-113.20</t>
+          <t>-111.27</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1134242083.377292</t>
+          <t>1135341687.642253</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>929280358.0</t>
+          <t>2352804551.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>651718545.6</v>
+        <v>1067809140.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>459389744.3</t>
+          <t>665737730.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>772359077.74</v>
+        <v>775901935.04</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>192328801</t>
+          <t>402071410</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-47189799.89088174</t>
+          <t>-15071192.86067748</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>35607688.27453578</t>
+          <t>161581145.8054459</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>929280358.0</t>
+          <t>2352804551.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20739.776</t>
+          <t>17888.375</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>44625</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1873,51 +1873,51 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>3.64</v>
+        <v>2.68</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.78</v>
+        <v>1.63</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.79000000000001</t>
+          <t>50.45</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.4</v>
+        <v>49.64</v>
       </c>
       <c r="AN4" t="n">
-        <v>52.35</v>
+        <v>52.11</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>62.45</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.07</v>
+        <v>-0.93</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-115.26</t>
+          <t>-113.20</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1134242083.377292</t>
+          <t>1135341687.642253</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1060885654.0</t>
+          <t>929280358.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>509324832.2</v>
+        <v>651718545.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>396320471.8</t>
+          <t>459389744.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>782128914.8200001</v>
+        <v>772359077.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>113004360</t>
+          <t>192328801</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-62243888.64823037</t>
+          <t>-47189799.89088174</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>6894352.184859514</t>
+          <t>35607688.27453578</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1060885654.0</t>
+          <t>929280358.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,24 +2102,24 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>51.8</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>51.6</t>
-        </is>
-      </c>
       <c r="CH4" t="inlineStr">
         <is>
           <t>31.98</t>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11750.074</t>
+          <t>20739.776</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.33</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>44625</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2295,51 +2295,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>2.31</v>
+        <v>3.64</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.15</v>
+        <v>0.78</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.79000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.19</v>
+        <v>49.4</v>
       </c>
       <c r="AN5" t="n">
-        <v>52.61</v>
+        <v>52.35</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.8</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.2</v>
+        <v>-1.07</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.08</t>
+          <t>-115.26</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1134242083.377292</t>
+          <t>1135341687.642253</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1060885654.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>361101851</v>
+        <v>509324832.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>320446639.8</t>
+          <t>396320471.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>788698875.08</v>
+        <v>782128914.8200001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>40655211</t>
+          <t>113004360</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-74814477.89061035</t>
+          <t>-62243888.64823037</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-48471493.66413736</t>
+          <t>6894352.184859514</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1060885654.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8142.579</t>
+          <t>11750.074</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-27.11</t>
+          <t>-25.33</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>44625</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.06</v>
+        <v>2.31</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.04</v>
+        <v>49.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>52.89</v>
+        <v>52.61</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.98</v>
+        <v>-0.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-118.51</t>
+          <t>-117.08</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1134242083.377292</t>
+          <t>1135341687.642253</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>303258012.4</v>
+        <v>361101851</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>304232232.7</t>
+          <t>320446639.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>833966853.42</v>
+        <v>788698875.08</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-974220</t>
+          <t>40655211</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-79604111.38633272</t>
+          <t>-74814477.89061035</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-75514297.49612796</t>
+          <t>-48471493.66413736</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,17 +2881,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5508.131</t>
+          <t>8142.579</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-27.04</t>
+          <t>-27.11</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>44625</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>49.12</v>
+        <v>49.04</v>
       </c>
       <c r="AN7" t="n">
-        <v>53.27</v>
+        <v>52.89</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.06</v>
+        <v>-0.98</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.38</v>
+        <v>-1.3</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-119.67</t>
+          <t>-118.51</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1134242083.377292</t>
+          <t>1135341687.642253</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>263666319.4</v>
+        <v>303258012.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>311360029.6</t>
+          <t>304232232.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>893391430.4</v>
+        <v>833966853.42</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-47693710</t>
+          <t>-974220</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-80347713.91182451</t>
+          <t>-79604111.38633272</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-91479905.38125283</t>
+          <t>-75514297.49612796</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3398,14 +3398,14 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4440.277</t>
+          <t>5508.131</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-23.09</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-27.04</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>44625</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>64.49</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-1.26</v>
+        <v>0.2</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>49.17</v>
+        <v>49.12</v>
       </c>
       <c r="AN8" t="n">
-        <v>53.68</v>
+        <v>53.27</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.16</v>
+        <v>-1.06</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.46</v>
+        <v>-1.38</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.81</t>
+          <t>-119.67</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1134242083.377292</t>
+          <t>1135341687.642253</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>267060943</v>
+        <v>263666319.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>347232794.8</t>
+          <t>311360029.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1007913686.44</v>
+        <v>893391430.4</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-80171851</t>
+          <t>-47693710</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-78323679.09920117</t>
+          <t>-80347713.91182451</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-96825149.70352924</t>
+          <t>-91479905.38125283</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>44625</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>64.49</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-0.29</v>
+        <v>-1.26</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.28</v>
+        <v>-0.1</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>49.23</v>
+        <v>49.17</v>
       </c>
       <c r="AN9" t="n">
-        <v>54.08</v>
+        <v>53.68</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.19</v>
+        <v>-1.16</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.54</v>
+        <v>-1.46</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-121.89</t>
+          <t>-120.81</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1134242083.377292</t>
+          <t>1135341687.642253</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>283316111.4</v>
+        <v>267060943</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>416505686.8</t>
+          <t>347232794.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1087982910.56</v>
+        <v>1007913686.44</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-133189575</t>
+          <t>-80171851</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-74959775.3529597</t>
+          <t>-78323679.09920117</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-95106052.24594092</t>
+          <t>-96825149.70352924</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>44625</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.29</v>
+        <v>-0.29</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.09</v>
+        <v>-0.28</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AN10" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.27</v>
+        <v>-1.19</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.63</v>
+        <v>-1.54</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1134242083.377292</t>
+          <t>1135341687.642253</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,24 +4634,24 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>48.95</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="CH10" t="inlineStr">
         <is>
           <t>31.98</t>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4681,42 +4681,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6085.789</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4211.204</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3.54</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>44625</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>59.82</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.45</v>
+        <v>2.29</v>
       </c>
       <c r="AI11" t="n">
-        <v>-2.01</v>
+        <v>-1.09</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-9.3</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>49.4</v>
+        <v>49.37</v>
       </c>
       <c r="AN11" t="n">
-        <v>54.69</v>
+        <v>54.43</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>16.10</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.44</v>
+        <v>-1.27</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.72</v>
+        <v>-1.63</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-124.40</t>
+          <t>-123.12</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1134242083.377292</t>
+          <t>1135341687.642253</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>305206453</v>
+        <v>279791428.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>528354756.8</t>
+          <t>472296995.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1193416018.88</v>
+        <v>1139949931.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-223148303</t>
+          <t>-192505566</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-66036000.73841473</t>
+          <t>-71296815.91787222</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-102070652.7246387</t>
+          <t>-100231299.4048884</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>302011850.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5896.567</t>
+          <t>4211.204</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-42.23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>44625</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5249,51 +5249,51 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>32.88</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AI12" t="n">
-        <v>-2.3</v>
+        <v>-2.01</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="AN12" t="n">
-        <v>55.04</v>
+        <v>54.69</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>55.71</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>16.10</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.56</v>
+        <v>-1.44</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.79</v>
+        <v>-1.72</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-125.39</t>
+          <t>-124.40</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1134242083.377292</t>
+          <t>1135341687.642253</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>359053739.8</v>
+        <v>305206453</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>779219302.6</t>
+          <t>528354756.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1233289107.3</v>
+        <v>1193416018.88</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-420165562</t>
+          <t>-223148303</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-59484245.83182855</t>
+          <t>-66036000.73841473</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-90860825.19125909</t>
+          <t>-102070652.7246387</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>289324693.0</t>
+          <t>206885633.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>30.06</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,17 +5478,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ12"/>
+  <dimension ref="A1:CR12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,320 +551,360 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>MA_last_cross_d2</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MA_last_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>MA_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -873,7 +913,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【x】看好</t>
+          <t>【d1】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24262.603</t>
+          <t>16550.342</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,395 +938,435 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>56.37</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-01-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>41.8</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-24.44</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-13.01</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/07/01</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>39.05</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>60.75</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-07-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-01-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>48.05</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-22.96</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-13.01</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13.94</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-1.89</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>9.51</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>-2.54</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>24263</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>90.91</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>-4.05</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>-8.84</t>
-        </is>
-      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>51.34</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>49.66</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>51.76</v>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>16550</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>71.43</t>
+        </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
+          <t>81.39</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-3.71</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>-9.14</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>51.46</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>51.59</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
           <t>56.78</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>87.16</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>94.04</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="BA2" t="inlineStr">
         <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-109.26</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-107.49</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>1135341687.642253</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>1276640741.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>1242168469.4</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>772713240.9</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>766248058.12</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>469455228</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>12633721.68434163</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>165010751.6819468</t>
-        </is>
-      </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1276640741.0</t>
+          <t>1135542601.565401</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
+          <t>852127658.0</t>
+        </is>
+      </c>
+      <c r="BF2" t="n">
+        <v>1294347792.4</v>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>827724821.7</t>
+        </is>
+      </c>
+      <c r="BH2" t="n">
+        <v>763148823</v>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>466622970</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>30912799.23728118</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>131447725.7784487</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>852127658.0</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>29.68</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>27.18</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>7.39</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>30.15</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>42602</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>50.5</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
         <is>
           <t>51.0</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1305,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44624.702</t>
+          <t>24262.603</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1410,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1420,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>60.39</t>
+          <t>60.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.59</t>
+          <t>-22.96</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,300 +1495,340 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025/07/01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>13.94</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>24263</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>72.73</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>16550</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>90.91</t>
         </is>
       </c>
-      <c r="AH3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>-4.44</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>-8.48</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>50.78</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>51.91</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>56.72</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>68.37</t>
-        </is>
+      <c r="AP3" t="n">
+        <v>1.29</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-0.79</v>
+        <v>3.38</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-4.05</t>
+        </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
+          <t>-8.84</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>51.34</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>51.76</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>56.78</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>87.16</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-111.27</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-109.26</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>1135341687.642253</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>2352804551.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>1067809140.8</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>665737730.1</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>775901935.04</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>402071410</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-15071192.86067748</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>161581145.8054459</t>
-        </is>
-      </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2352804551.0</t>
+          <t>1135542601.565401</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
+          <t>1276640741.0</t>
+        </is>
+      </c>
+      <c r="BF3" t="n">
+        <v>1242168469.4</v>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>772713240.9</t>
+        </is>
+      </c>
+      <c r="BH3" t="n">
+        <v>766248058.12</v>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>469455228</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>12633721.68434163</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>165010751.6819468</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>1276640741.0</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>26.93</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>29.68</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>7.39</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>30.15</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>42602</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>55.2</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>50.7</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>51.2</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1727,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17888.375</t>
+          <t>44624.702</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1872,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1882,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>60.39</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-24.59</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,300 +1957,340 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025/07/01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>25.65</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-8.05</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>24263</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-4.74</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>-7.96</t>
-        </is>
-      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>50.45</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>49.64</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>52.11</v>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>16550</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>72.73</t>
+        </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>56.62</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>62.45</t>
-        </is>
+          <t>90.91</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-0.93</v>
+        <v>2.37</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-4.44</t>
+        </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
+          <t>-8.48</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>50.78</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>51.91</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>56.72</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>68.37</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-113.20</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-111.27</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>1135341687.642253</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>929280358.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>651718545.6</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>459389744.3</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>772359077.74</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>192328801</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-47189799.89088174</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>35607688.27453578</t>
-        </is>
-      </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>929280358.0</t>
+          <t>1135542601.565401</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
+          <t>2352804551.0</t>
+        </is>
+      </c>
+      <c r="BF4" t="n">
+        <v>1067809140.8</v>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>665737730.1</t>
+        </is>
+      </c>
+      <c r="BH4" t="n">
+        <v>775901935.04</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>402071410</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>-15071192.86067748</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>161581145.8054459</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>2352804551.0</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>29.18</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>26.93</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>價跌量增</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>7.39</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>30.15</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>42602</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>51.1</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>51.8</t>
-        </is>
-      </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>55.2</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>50.7</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2149,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20739.776</t>
+          <t>17888.375</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2334,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2344,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,300 +2419,340 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025/07/01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>10.28</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>24263</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>16550</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>89.13</t>
-        </is>
-      </c>
-      <c r="AH5" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>-5.62</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>-7.36</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>49.79000000000001</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>52.35</v>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>47.84</t>
-        </is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.68</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-1.07</v>
+        <v>1.63</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-4.74</t>
+        </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
+          <t>-7.96</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>50.45</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>52.11</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>56.62</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>62.45</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-115.26</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-113.20</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>1135341687.642253</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>1060885654.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>509324832.2</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>396320471.8</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>782128914.8200001</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>113004360</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-62243888.64823037</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>6894352.184859514</t>
-        </is>
-      </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1060885654.0</t>
+          <t>1135542601.565401</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
+          <t>929280358.0</t>
+        </is>
+      </c>
+      <c r="BF5" t="n">
+        <v>651718545.6</v>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>459389744.3</t>
+        </is>
+      </c>
+      <c r="BH5" t="n">
+        <v>772359077.74</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>192328801</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>-47189799.89088174</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>35607688.27453578</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>929280358.0</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>28.68</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>29.18</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>7.39</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>30.15</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>42602</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
         <is>
           <t>51.8</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>51.6</t>
-        </is>
-      </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2571,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11750.074</t>
+          <t>20739.776</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2796,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2806,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.33</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,300 +2881,340 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025/07/01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>11.92</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>24263</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>16550</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>78.99</t>
-        </is>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>-6.5</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>-6.72</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>49.26000000000001</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>49.19</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>52.61</v>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>56.4</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
+          <t>89.13</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>3.64</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-1.2</v>
+        <v>0.78</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-5.62</t>
+        </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
+          <t>-7.36</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>49.79000000000001</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>47.84</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-117.08</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-115.26</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>1135341687.642253</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>591231043.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>361101851</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>320446639.8</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>788698875.08</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>40655211</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-74814477.89061035</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-48471493.66413736</t>
-        </is>
-      </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1135542601.565401</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
+          <t>1060885654.0</t>
+        </is>
+      </c>
+      <c r="BF6" t="n">
+        <v>509324832.2</v>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>396320471.8</t>
+        </is>
+      </c>
+      <c r="BH6" t="n">
+        <v>782128914.8200001</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>113004360</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>-62243888.64823037</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>6894352.184859514</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>1060885654.0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>25.69</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>28.68</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>7.39</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>30.15</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>42602</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>49.3</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>51.6</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2993,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8142.579</t>
+          <t>11750.074</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3258,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3268,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-27.11</t>
+          <t>-25.33</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,300 +3343,340 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025/07/01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>24263</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>67.39</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>57.97</t>
-        </is>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>-7.28</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>-6.06</t>
-        </is>
-      </c>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.17</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>49.04</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>52.89</v>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>16550</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>56.3</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>25.08</t>
-        </is>
+          <t>78.99</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.31</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-1.3</v>
+        <v>0.15</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
+          <t>-6.72</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>49.26000000000001</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>49.19</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-118.51</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-117.08</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>1135341687.642253</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>404844098.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>303258012.4</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>304232232.7</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>833966853.42</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-974220</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-79604111.38633272</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-75514297.49612796</t>
-        </is>
-      </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>1135542601.565401</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
+          <t>591231043.0</t>
+        </is>
+      </c>
+      <c r="BF7" t="n">
+        <v>361101851</v>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>320446639.8</t>
+        </is>
+      </c>
+      <c r="BH7" t="n">
+        <v>788698875.08</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>40655211</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>-74814477.89061035</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>-48471493.66413736</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>591231043.0</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>22.69</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>25.69</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>7.39</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>30.15</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>42602</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>50.5</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>49.2</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>49.2</t>
-        </is>
-      </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>49.3</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>48.85</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3415,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5508.131</t>
+          <t>8142.579</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3720,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3730,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-27.04</t>
+          <t>-27.11</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,300 +3805,340 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025/07/01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>4.68</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-2.64</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>24263</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>69.57</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>54.35</t>
-        </is>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-7.8</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>-5.21</t>
-        </is>
-      </c>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.15</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>49.12</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>53.27</v>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>16550</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>67.39</t>
+        </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>56.2</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>23.29</t>
-        </is>
+          <t>57.97</t>
+        </is>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.06</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-1.38</v>
+        <v>0.26</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-7.28</t>
+        </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
+          <t>-6.06</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>49.17</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>49.04</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>52.89</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>56.3</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>25.08</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-119.67</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-118.51</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>1135341687.642253</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>272351575.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>263666319.4</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>311360029.6</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>893391430.4</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-47693710</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-80347713.91182451</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-91479905.38125283</t>
-        </is>
-      </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>1135542601.565401</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
+          <t>404844098.0</t>
+        </is>
+      </c>
+      <c r="BF8" t="n">
+        <v>303258012.4</v>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>304232232.7</t>
+        </is>
+      </c>
+      <c r="BH8" t="n">
+        <v>833966853.42</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>-974220</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>-79604111.38633272</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>-75514297.49612796</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>404844098.0</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>22.82</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>22.69</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>1.54</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>7.39</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>30.15</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>42602</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>49.0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>49.0</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>49.25</t>
-        </is>
-      </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>50.5</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3827,7 +4147,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4440.277</t>
+          <t>5508.131</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +4182,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +4192,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-23.09</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-27.04</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,300 +4267,340 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025/07/01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>-0.61</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>24263</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>36.96</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>64.49</t>
-        </is>
-      </c>
-      <c r="AH9" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>-8.4</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>-4.31</t>
-        </is>
-      </c>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49.12</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
-        <v>49.17</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>53.68</v>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>16550</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>69.57</t>
+        </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>56.1</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>20.72</t>
-        </is>
+          <t>54.35</t>
+        </is>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>-1.46</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-7.8</t>
+        </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
+          <t>-5.21</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>53.27</v>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>23.29</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-120.81</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-119.67</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>1135341687.642253</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>217311791.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>267060943</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>347232794.8</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1007913686.44</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-80171851</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-78323679.09920117</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-96825149.70352924</t>
-        </is>
-      </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>1135542601.565401</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
+          <t>272351575.0</t>
+        </is>
+      </c>
+      <c r="BF9" t="n">
+        <v>263666319.4</v>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>311360029.6</t>
+        </is>
+      </c>
+      <c r="BH9" t="n">
+        <v>893391430.4</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>-47693710</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>-80347713.91182451</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>-91479905.38125283</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>272351575.0</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>20.95</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>22.82</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>7.39</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>30.15</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>42602</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>49.45</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>49.25</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4259,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4644,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4654,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,300 +4729,340 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025/07/01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-1.65</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>24263</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>56.52</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>65.42</t>
-        </is>
-      </c>
-      <c r="AH10" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>-8.97</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>-3.44</t>
-        </is>
-      </c>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49.09</t>
-        </is>
-      </c>
-      <c r="AM10" t="n">
-        <v>49.23</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>54.08</v>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>16550</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>36.96</t>
+        </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>56.01</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>22.44</t>
-        </is>
+          <t>64.49</t>
+        </is>
+      </c>
+      <c r="AP10" t="n">
+        <v>-1.26</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-1.54</v>
+        <v>-0.1</v>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-8.4</t>
+        </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
+          <t>-4.31</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>49.12</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>56.1</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>20.72</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-121.89</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-120.81</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>1135341687.642253</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>319770748.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>283316111.4</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>416505686.8</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1087982910.56</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-133189575</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-74959775.3529597</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-95106052.24594092</t>
-        </is>
-      </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>1135542601.565401</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
+          <t>217311791.0</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>267060943</v>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>347232794.8</t>
+        </is>
+      </c>
+      <c r="BH10" t="n">
+        <v>1007913686.44</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-80171851</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>-78323679.09920117</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>-96825149.70352924</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>217311791.0</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>22.07</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>20.95</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BR10" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>7.39</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>30.15</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>42602</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>48.95</t>
-        </is>
-      </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>49.45</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>48.25</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4681,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +5106,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +5116,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,300 +5191,340 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025/07/01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-2.25</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>24263</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>59.82</t>
-        </is>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>-9.3</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-2.66</t>
-        </is>
-      </c>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>48.83</t>
-        </is>
-      </c>
-      <c r="AM11" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>54.43</v>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>16550</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>56.52</t>
+        </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>55.92</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>22.18</t>
-        </is>
+          <t>65.42</t>
+        </is>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0.29</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>-1.63</v>
+        <v>-0.28</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-8.97</t>
+        </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
+          <t>-3.44</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>49.09</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>56.01</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>22.44</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-123.12</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-121.89</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>1135341687.642253</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>302011850.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>279791428.6</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>472296995.2</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1139949931.8</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-192505566</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-71296815.91787222</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>-100231299.4048884</t>
-        </is>
-      </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>1135542601.565401</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
+          <t>319770748.0</t>
+        </is>
+      </c>
+      <c r="BF11" t="n">
+        <v>283316111.4</v>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>416505686.8</t>
+        </is>
+      </c>
+      <c r="BH11" t="n">
+        <v>1087982910.56</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>-133189575</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>-74959775.3529597</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>-95106052.24594092</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>319770748.0</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>24.56</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>22.07</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BR11" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>7.39</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>30.15</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>42602</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
         <is>
           <t>48.95</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5103,42 +5543,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6085.789</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4211.204</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>5.58</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-42.23</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-26.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,300 +5653,340 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025/07/01</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>24263</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>39.73</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>32.88</t>
-        </is>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>-9.69</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>-2.01</t>
-        </is>
-      </c>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>48.4</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>54.69</v>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>16550</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>55.82</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>16.10</t>
-        </is>
+          <t>59.82</t>
+        </is>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.29</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-1.72</v>
+        <v>-1.09</v>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-9.3</t>
+        </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
+          <t>-2.66</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>48.83</t>
+        </is>
+      </c>
+      <c r="AU12" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>55.92</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>22.18</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-124.40</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-123.12</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>1135341687.642253</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>206885633.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>305206453</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>528354756.8</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1193416018.88</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-223148303</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-66036000.73841473</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-102070652.7246387</t>
-        </is>
-      </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>206885633.0</t>
+          <t>1135542601.565401</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
+          <t>302011850.0</t>
+        </is>
+      </c>
+      <c r="BF12" t="n">
+        <v>279791428.6</v>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>472296995.2</t>
+        </is>
+      </c>
+      <c r="BH12" t="n">
+        <v>1139949931.8</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>-192505566</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>-71296815.91787222</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>-100231299.4048884</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>302011850.0</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>22.44</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>24.56</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BR12" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>7.54</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>7.39</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>30.15</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>42602</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>49.5</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>49.5</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="CN12" t="inlineStr">
+        <is>
+          <t>48.95</t>
+        </is>
+      </c>
+      <c r="CO12" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="CP12" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16550.342</t>
+          <t>6918.145</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>56.37</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.44</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,66 +1094,66 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>81.39</t>
+          <t>67.86</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>-0.89</v>
+        <v>-2.07</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-9.35</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>51.46</t>
+          <t>51.16</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>49.67</v>
+        <v>49.61</v>
       </c>
       <c r="AV2" t="n">
-        <v>51.59</v>
+        <v>51.39</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>56.78</t>
+          <t>56.69</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>94.04</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.53</v>
+        <v>-0.43</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-107.49</t>
+          <t>-106.17</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1135542601.565401</t>
+          <t>1134677799.139045</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>852127658.0</t>
+          <t>346535516.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>1294347792.4</v>
+        <v>1151477764.8</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>827724821.7</t>
+          <t>830401298.5</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>763148823</v>
+        <v>751453437.48</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>466622970</t>
+          <t>321076466</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>30912799.23728118</t>
+          <t>36425907.63947468</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>131447725.7784487</t>
+          <t>66748003.8515389</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>852127658.0</t>
+          <t>346535516.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1273,17 +1273,17 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>42602</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24262.603</t>
+          <t>16550.342</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,124 +1400,124 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>56.37</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-01-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>41.8</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-24.44</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-13.01</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/07/01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>39.05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-1.96</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>60.75</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-07-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-01-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>48.05</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-22.96</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-13.01</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/07/01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="AD3" t="inlineStr">
         <is>
           <t>2025/07/03</t>
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,50 +1556,50 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>81.39</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>1.29</v>
+        <v>-0.89</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>51.34</t>
+          <t>51.46</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>49.66</v>
+        <v>49.67</v>
       </c>
       <c r="AV3" t="n">
-        <v>51.76</v>
+        <v>51.59</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1608,14 +1608,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>87.16</t>
+          <t>94.04</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.65</v>
+        <v>-0.53</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-107.49</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1135542601.565401</t>
+          <t>1134677799.139045</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>1276640741.0</t>
+          <t>852127658.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>1242168469.4</v>
+        <v>1294347792.4</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>772713240.9</t>
+          <t>827724821.7</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>766248058.12</v>
+        <v>763148823</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>469455228</t>
+          <t>466622970</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>12633721.68434163</t>
+          <t>30912799.23728118</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>165010751.6819468</t>
+          <t>131447725.7784487</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1276640741.0</t>
+          <t>852127658.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>42602</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
+          <t>50.5</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
           <t>51.0</t>
-        </is>
-      </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>52.0</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44624.702</t>
+          <t>24262.603</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.39</t>
+          <t>60.75</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.59</t>
+          <t>-22.96</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,17 +2018,17 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2037,47 +2037,47 @@
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>0.24</v>
+        <v>1.29</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.37</v>
+        <v>3.38</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>51.34</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>49.6</v>
+        <v>49.66</v>
       </c>
       <c r="AV4" t="n">
-        <v>51.91</v>
+        <v>51.76</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>56.78</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>87.16</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>-0.25</v>
+        <v>-0.08</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.79</v>
+        <v>-0.65</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-111.27</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1135542601.565401</t>
+          <t>1134677799.139045</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2352804551.0</t>
+          <t>1276640741.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>1067809140.8</v>
+        <v>1242168469.4</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>665737730.1</t>
+          <t>772713240.9</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>775901935.04</v>
+        <v>766248058.12</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>402071410</t>
+          <t>469455228</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-15071192.86067748</t>
+          <t>12633721.68434163</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>161581145.8054459</t>
+          <t>165010751.6819468</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>2352804551.0</t>
+          <t>1276640741.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2197,17 +2197,17 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>42602</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17888.375</t>
+          <t>44624.702</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>60.39</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-24.59</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,66 +2480,66 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>2.68</v>
+        <v>0.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.63</v>
+        <v>2.37</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>50.45</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>49.64</v>
+        <v>49.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>52.11</v>
+        <v>51.91</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>56.72</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>62.45</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>-0.35</v>
+        <v>-0.25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.93</v>
+        <v>-0.79</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-113.20</t>
+          <t>-111.27</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1135542601.565401</t>
+          <t>1134677799.139045</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>929280358.0</t>
+          <t>2352804551.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>651718545.6</v>
+        <v>1067809140.8</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>459389744.3</t>
+          <t>665737730.1</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>772359077.74</v>
+        <v>775901935.04</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>192328801</t>
+          <t>402071410</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-47189799.89088174</t>
+          <t>-15071192.86067748</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>35607688.27453578</t>
+          <t>161581145.8054459</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>929280358.0</t>
+          <t>2352804551.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2659,17 +2659,17 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>42602</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20739.776</t>
+          <t>17888.375</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,12 +2942,12 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2957,51 +2957,51 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>3.64</v>
+        <v>2.68</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.78</v>
+        <v>1.63</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>49.79000000000001</t>
+          <t>50.45</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>49.4</v>
+        <v>49.64</v>
       </c>
       <c r="AV6" t="n">
-        <v>52.35</v>
+        <v>52.11</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>62.45</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-1.07</v>
+        <v>-0.93</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-115.26</t>
+          <t>-113.20</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1135542601.565401</t>
+          <t>1134677799.139045</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>1060885654.0</t>
+          <t>929280358.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>509324832.2</v>
+        <v>651718545.6</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>396320471.8</t>
+          <t>459389744.3</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>782128914.8200001</v>
+        <v>772359077.74</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>113004360</t>
+          <t>192328801</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-62243888.64823037</t>
+          <t>-47189799.89088174</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>6894352.184859514</t>
+          <t>35607688.27453578</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1060885654.0</t>
+          <t>929280358.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>42602</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
           <t>51.8</t>
-        </is>
-      </c>
-      <c r="CN6" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="CO6" t="inlineStr">
-        <is>
-          <t>51.6</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11750.074</t>
+          <t>20739.776</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.33</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,12 +3404,12 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3419,51 +3419,51 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>2.31</v>
+        <v>3.64</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.15</v>
+        <v>0.78</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.79000000000001</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>49.19</v>
+        <v>49.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>52.61</v>
+        <v>52.35</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>-0.8</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-1.2</v>
+        <v>-1.07</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-117.08</t>
+          <t>-115.26</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1135542601.565401</t>
+          <t>1134677799.139045</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1060885654.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>361101851</v>
+        <v>509324832.2</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>320446639.8</t>
+          <t>396320471.8</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>788698875.08</v>
+        <v>782128914.8200001</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>40655211</t>
+          <t>113004360</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-74814477.89061035</t>
+          <t>-62243888.64823037</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-48471493.66413736</t>
+          <t>6894352.184859514</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1060885654.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3583,17 +3583,17 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>42602</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8142.579</t>
+          <t>11750.074</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-27.11</t>
+          <t>-25.33</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,66 +3866,66 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>0.06</v>
+        <v>2.31</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>49.04</v>
+        <v>49.19</v>
       </c>
       <c r="AV8" t="n">
-        <v>52.89</v>
+        <v>52.61</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>-0.98</v>
+        <v>-0.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-118.51</t>
+          <t>-117.08</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1135542601.565401</t>
+          <t>1134677799.139045</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>303258012.4</v>
+        <v>361101851</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>304232232.7</t>
+          <t>320446639.8</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>833966853.42</v>
+        <v>788698875.08</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-974220</t>
+          <t>40655211</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-79604111.38633272</t>
+          <t>-74814477.89061035</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-75514297.49612796</t>
+          <t>-48471493.66413736</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>42602</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5508.131</t>
+          <t>8142.579</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-27.04</t>
+          <t>-27.11</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,66 +4328,66 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>49.12</v>
+        <v>49.04</v>
       </c>
       <c r="AV9" t="n">
-        <v>53.27</v>
+        <v>52.89</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>-1.06</v>
+        <v>-0.98</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-1.38</v>
+        <v>-1.3</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-119.67</t>
+          <t>-118.51</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1135542601.565401</t>
+          <t>1134677799.139045</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>263666319.4</v>
+        <v>303258012.4</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>311360029.6</t>
+          <t>304232232.7</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>893391430.4</v>
+        <v>833966853.42</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-47693710</t>
+          <t>-974220</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-80347713.91182451</t>
+          <t>-79604111.38633272</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-91479905.38125283</t>
+          <t>-75514297.49612796</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>42602</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4609,7 +4609,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4440.277</t>
+          <t>5508.131</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-23.09</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-27.04</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,66 +4790,66 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>64.49</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>-1.26</v>
+        <v>0.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>49.17</v>
+        <v>49.12</v>
       </c>
       <c r="AV10" t="n">
-        <v>53.68</v>
+        <v>53.27</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>-1.16</v>
+        <v>-1.06</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-1.46</v>
+        <v>-1.38</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-120.81</t>
+          <t>-119.67</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1135542601.565401</t>
+          <t>1134677799.139045</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>267060943</v>
+        <v>263666319.4</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>347232794.8</t>
+          <t>311360029.6</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>1007913686.44</v>
+        <v>893391430.4</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-80171851</t>
+          <t>-47693710</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-78323679.09920117</t>
+          <t>-80347713.91182451</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-96825149.70352924</t>
+          <t>-91479905.38125283</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>42602</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,22 +5034,22 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,66 +5252,66 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>64.49</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>-0.29</v>
+        <v>-1.26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.28</v>
+        <v>-0.1</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>49.23</v>
+        <v>49.17</v>
       </c>
       <c r="AV11" t="n">
-        <v>54.08</v>
+        <v>53.68</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>-1.19</v>
+        <v>-1.16</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-1.54</v>
+        <v>-1.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-121.89</t>
+          <t>-120.81</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1135542601.565401</t>
+          <t>1134677799.139045</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>283316111.4</v>
+        <v>267060943</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>416505686.8</t>
+          <t>347232794.8</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>1087982910.56</v>
+        <v>1007913686.44</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-133189575</t>
+          <t>-80171851</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-74959775.3529597</t>
+          <t>-78323679.09920117</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-95106052.24594092</t>
+          <t>-96825149.70352924</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>42602</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6085.789</t>
+          <t>6477.386</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-31.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-26.00</t>
+          <t>-27.48</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,66 +5714,66 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>59.82</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>2.29</v>
+        <v>-0.29</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.09</v>
+        <v>-0.28</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-8.97</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>49.09</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>49.37</v>
+        <v>49.23</v>
       </c>
       <c r="AV12" t="n">
-        <v>54.43</v>
+        <v>54.08</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.44</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>-1.27</v>
+        <v>-1.19</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-1.63</v>
+        <v>-1.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-123.12</t>
+          <t>-121.89</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1135542601.565401</t>
+          <t>1134677799.139045</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>279791428.6</v>
+        <v>283316111.4</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>472296995.2</t>
+          <t>416505686.8</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>1139949931.8</v>
+        <v>1087982910.56</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-192505566</t>
+          <t>-133189575</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-71296815.91787222</t>
+          <t>-74959775.3529597</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>-100231299.4048884</t>
+          <t>-95106052.24594092</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>302011850.0</t>
+          <t>319770748.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>22.07</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>42602</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="CO12" t="inlineStr">
+        <is>
           <t>48.95</t>
-        </is>
-      </c>
-      <c r="CO12" t="inlineStr">
-        <is>
-          <t>49.95</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>39.1</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>3.98</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>6918</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>32.14</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>67.86</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>-2.07</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>3.12</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>-3.46</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>-9.35</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>51.16</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>49.61</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>51.39</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>56.69</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>85.74</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>-0.43</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-106.17</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>1134677799.139045</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>346535516.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>1151477764.8</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>830401298.5</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>751453437.48</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>321076466</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>36425907.63947468</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>66748003.8515389</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>346535516.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>24.94</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>1.57</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>7.26</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>30.53</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>41850</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>50.4</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>50.5</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>50.1</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>39.1</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>9.51</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>-2.54</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>6918</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>71.43</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>81.39</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>-0.89</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>3.6</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>-3.71</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>-9.14</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>51.46</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>49.67</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>51.59</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>56.78</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>94.04</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>-0.53</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-107.49</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>1134677799.139045</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>852127658.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>1294347792.4</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>827724821.7</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>763148823</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>466622970</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>30912799.23728118</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>131447725.7784487</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>852127658.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>27.18</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>1.59</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>7.26</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>30.53</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>41850</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>52.5</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>50.5</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>51.0</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>39.1</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>13.94</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>-1.89</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>6918</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>90.91</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>1.29</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>3.38</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>-4.05</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>-8.84</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>51.34</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>49.66</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>51.76</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>56.78</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>87.16</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-0.65</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-109.26</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>1134677799.139045</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>1276640741.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>1242168469.4</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>772713240.9</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>766248058.12</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>469455228</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>12633721.68434163</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>165010751.6819468</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>1276640741.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>29.68</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>1.63</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>7.26</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>30.53</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>41850</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>51.2</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>54.0</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>51.0</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>39.1</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>25.65</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>-8.05</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>6918</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>72.73</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>90.91</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>0.24</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>2.37</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>-4.44</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>-8.48</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>50.78</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>49.6</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>51.91</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>56.72</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>68.37</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>-0.79</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-111.27</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>1134677799.139045</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>2352804551.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>1067809140.8</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>665737730.1</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>775901935.04</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>402071410</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-15071192.86067748</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>161581145.8054459</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>2352804551.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>26.93</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價跌量增</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>1.59</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>7.26</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>30.53</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>41850</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>55.2</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>50.7</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>50.9</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>39.1</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>10.28</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>6918</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>2.68</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>1.63</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-4.74</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>-7.96</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>50.45</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>49.64</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>52.11</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>56.62</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>62.45</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>-0.35</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-0.93</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-113.20</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>1134677799.139045</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>929280358.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>651718545.6</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>459389744.3</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>772359077.74</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>192328801</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-47189799.89088174</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>35607688.27453578</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>929280358.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>29.18</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>7.26</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>30.53</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>41850</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>51.0</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>51.8</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>39.1</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>11.92</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>2.40</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>6918</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>89.13</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>3.64</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>0.78</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-5.62</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>-7.36</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>49.79000000000001</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>49.4</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>52.35</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>56.5</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>47.84</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>-1.07</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-115.26</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>1134677799.139045</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>1060885654.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>509324832.2</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>396320471.8</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>782128914.8200001</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>113004360</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-62243888.64823037</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>6894352.184859514</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>1060885654.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>28.68</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>7.26</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>30.53</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>41850</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>51.5</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>51.8</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>50.2</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>51.6</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>39.1</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>6.75</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>-0.00</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>6918</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>78.99</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>2.31</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>0.15</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-6.5</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>-6.72</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>49.26000000000001</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>49.19</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>52.61</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>56.4</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>33.33</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>-0.8</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>-1.2</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-117.08</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>1134677799.139045</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>591231043.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>361101851</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>320446639.8</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>788698875.08</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>40655211</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-74814477.89061035</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-48471493.66413736</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>591231043.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>25.69</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>1.58</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>7.26</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>30.53</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>41850</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>49.3</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>48.85</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>50.4</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>39.1</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>4.68</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>-2.64</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>6918</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>67.39</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>57.97</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>0.06</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>0.26</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-7.28</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>-6.06</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>49.17</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>49.04</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>52.89</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>56.3</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>25.08</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>-0.98</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-118.51</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>1134677799.139045</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>404844098.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>303258012.4</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>304232232.7</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>833966853.42</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-974220</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-79604111.38633272</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-75514297.49612796</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>404844098.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>22.69</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>1.54</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>7.26</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>30.53</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>41850</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>50.5</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>49.2</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>49.2</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>39.1</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-0.61</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>6918</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>69.57</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>54.35</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>0.2</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-7.8</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>-5.21</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>49.12</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>53.27</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>56.2</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>23.29</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>-1.06</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-1.38</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-119.67</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>1134677799.139045</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>272351575.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>263666319.4</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>311360029.6</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>893391430.4</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-47693710</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-80347713.91182451</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-91479905.38125283</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>272351575.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>22.82</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>1.54</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>7.26</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>30.53</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>41850</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>49.0</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>49.8</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>49.0</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>49.25</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>39.1</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>2.55</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-1.65</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>6918</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>36.96</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>64.49</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>-1.26</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-8.4</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>-4.31</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>49.12</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>49.17</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>53.68</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>56.1</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>20.72</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>-1.16</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-1.46</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-120.81</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>1134677799.139045</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>217311791.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>267060943</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>347232794.8</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>1007913686.44</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>-80171851</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-78323679.09920117</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-96825149.70352924</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>217311791.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>20.95</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>7.26</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>30.53</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>41850</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>49.45</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>48.25</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>48.5</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/10/20</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/07/03</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>39.1</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-2.25</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>6918</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>56.52</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>65.42</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-0.28</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-8.97</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>-3.44</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>49.09</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>49.23</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>54.08</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>56.01</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>22.44</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>-1.19</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-1.54</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>7.04</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-121.89</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/11/12</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>1134677799.139045</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>319770748.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>283316111.4</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>416505686.8</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>1087982910.56</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>-133189575</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-74959775.3529597</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-95106052.24594092</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>319770748.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>40.1</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/07/24</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>22.07</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>宏達電</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>通信網路業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-36.86822403006653</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>-14.58459224643812</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>-2.04560003730758</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>7.26</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>35.20%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>-119.21%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>30.53</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>41850</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>虛擬實境裝置,智慧型手持式87.83%、其他12.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>宏達電-通信網路業-上市</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>50.2</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>48.8</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>48.95</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>31.98</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 通信網路 - 無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 文化創意業 - 廣播電視/電影產業、數位內容產業、流行音樂及文化內容產業** 區塊鏈 - 商業應用、開發工具** 人工智慧 - 領域解決方案、機器學習、雲端平台、資料處理** 體驗科技 - 頭顯裝置品牌廠、硬體開發工具、軟體開發工具、技術標準/聯盟、應用軟體/內容、VR Headset、AR Smart Glasses、MR Headset &amp; SG、Qualcomm XR Platform、工作流程創建、內容管理與創建、3D工具、培訓、會議、工作流程引導、地圖、遊戲、其他** 運動科技 - 穿戴式裝置、數位內容</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6918.145</t>
+          <t>9557.26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-26.81</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>67.86</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-2.07</v>
+        <v>-2.53</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.12</v>
+        <v>2.1</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-9.66</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>51.16</t>
+          <t>50.68</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>49.61</v>
+        <v>49.64</v>
       </c>
       <c r="AZ2" t="n">
-        <v>51.39</v>
+        <v>51.16</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>56.69</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>62.47</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.43</v>
+        <v>-0.38</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-106.17</t>
+          <t>-105.34</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1134677799.139045</t>
+          <t>1134076721.703366</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>346535516.0</t>
+          <t>470739725.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>1151477764.8</v>
+        <v>1059769638.2</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>830401298.5</t>
+          <t>855744091.9</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>751453437.48</v>
+        <v>721014826.84</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>321076466</t>
+          <t>204025546</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>36425907.63947468</t>
+          <t>35299585.55361911</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>66748003.8515389</t>
+          <t>29104814.08141351</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>346535516.0</t>
+          <t>470739725.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41266</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16550.342</t>
+          <t>6918.145</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>56.37</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.44</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>81.39</t>
+          <t>67.86</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-0.89</v>
+        <v>-2.07</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-9.35</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>51.46</t>
+          <t>51.16</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>49.67</v>
+        <v>49.61</v>
       </c>
       <c r="AZ3" t="n">
-        <v>51.59</v>
+        <v>51.39</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>56.78</t>
+          <t>56.69</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>94.04</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.53</v>
+        <v>-0.43</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-107.49</t>
+          <t>-106.17</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1134677799.139045</t>
+          <t>1134076721.703366</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>852127658.0</t>
+          <t>346535516.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>1294347792.4</v>
+        <v>1151477764.8</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>827724821.7</t>
+          <t>830401298.5</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>763148823</v>
+        <v>751453437.48</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>466622970</t>
+          <t>321076466</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>30912799.23728118</t>
+          <t>36425907.63947468</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>131447725.7784487</t>
+          <t>66748003.8515389</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>852127658.0</t>
+          <t>346535516.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41266</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24262.603</t>
+          <t>16550.342</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,172 +1922,172 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-3.24</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>56.37</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-01-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>41.8</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-24.44</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-13.01</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/07/01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>39.05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-3.79</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>60.75</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-07-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-01-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>67.5</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>48.05</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-22.96</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-13.01</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/07/01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/07/03</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>39.1</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/09/10</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,50 +2098,50 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>81.39</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1.29</v>
+        <v>-0.89</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>51.34</t>
+          <t>51.46</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>49.66</v>
+        <v>49.67</v>
       </c>
       <c r="AZ4" t="n">
-        <v>51.76</v>
+        <v>51.59</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2150,14 +2150,14 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>87.16</t>
+          <t>94.04</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.65</v>
+        <v>-0.53</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-107.49</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1134677799.139045</t>
+          <t>1134076721.703366</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>1276640741.0</t>
+          <t>852127658.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>1242168469.4</v>
+        <v>1294347792.4</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>772713240.9</t>
+          <t>827724821.7</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>766248058.12</v>
+        <v>763148823</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>469455228</t>
+          <t>466622970</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>12633721.68434163</t>
+          <t>30912799.23728118</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>165010751.6819468</t>
+          <t>131447725.7784487</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>1276640741.0</t>
+          <t>852127658.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41266</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
+          <t>50.5</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
           <t>51.0</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>52.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44624.702</t>
+          <t>24262.603</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>60.39</t>
+          <t>60.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.59</t>
+          <t>-22.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,17 +2580,17 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2599,47 +2599,47 @@
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.24</v>
+        <v>1.29</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.37</v>
+        <v>3.38</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>51.34</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>49.6</v>
+        <v>49.66</v>
       </c>
       <c r="AZ5" t="n">
-        <v>51.91</v>
+        <v>51.76</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>56.78</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>87.16</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.25</v>
+        <v>-0.08</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.79</v>
+        <v>-0.65</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-111.27</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1134677799.139045</t>
+          <t>1134076721.703366</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>2352804551.0</t>
+          <t>1276640741.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>1067809140.8</v>
+        <v>1242168469.4</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>665737730.1</t>
+          <t>772713240.9</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>775901935.04</v>
+        <v>766248058.12</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>402071410</t>
+          <t>469455228</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-15071192.86067748</t>
+          <t>12633721.68434163</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>161581145.8054459</t>
+          <t>165010751.6819468</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>2352804551.0</t>
+          <t>1276640741.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41266</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17888.375</t>
+          <t>44624.702</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>60.39</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-24.59</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>2.68</v>
+        <v>0.24</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.63</v>
+        <v>2.37</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>50.45</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>49.64</v>
+        <v>49.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>52.11</v>
+        <v>51.91</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>56.72</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>62.45</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.35</v>
+        <v>-0.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.93</v>
+        <v>-0.79</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-113.20</t>
+          <t>-111.27</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1134677799.139045</t>
+          <t>1134076721.703366</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>929280358.0</t>
+          <t>2352804551.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>651718545.6</v>
+        <v>1067809140.8</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>459389744.3</t>
+          <t>665737730.1</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>772359077.74</v>
+        <v>775901935.04</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>192328801</t>
+          <t>402071410</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-47189799.89088174</t>
+          <t>-15071192.86067748</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>35607688.27453578</t>
+          <t>161581145.8054459</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>929280358.0</t>
+          <t>2352804551.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,17 +3241,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41266</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20739.776</t>
+          <t>17888.375</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-4.86</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,12 +3544,12 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3559,51 +3559,51 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>3.64</v>
+        <v>2.68</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.78</v>
+        <v>1.63</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>49.79000000000001</t>
+          <t>50.45</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>49.4</v>
+        <v>49.64</v>
       </c>
       <c r="AZ7" t="n">
-        <v>52.35</v>
+        <v>52.11</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>62.45</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="BD7" t="n">
-        <v>-1.07</v>
+        <v>-0.93</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-115.26</t>
+          <t>-113.20</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1134677799.139045</t>
+          <t>1134076721.703366</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>1060885654.0</t>
+          <t>929280358.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>509324832.2</v>
+        <v>651718545.6</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>396320471.8</t>
+          <t>459389744.3</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>782128914.8200001</v>
+        <v>772359077.74</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>113004360</t>
+          <t>192328801</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-62243888.64823037</t>
+          <t>-47189799.89088174</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>6894352.184859514</t>
+          <t>35607688.27453578</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>1060885654.0</t>
+          <t>929280358.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41266</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
           <t>51.8</t>
-        </is>
-      </c>
-      <c r="CR7" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="CS7" t="inlineStr">
-        <is>
-          <t>51.6</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11750.074</t>
+          <t>20739.776</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-25.33</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4041,51 +4041,51 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>2.31</v>
+        <v>3.64</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.15</v>
+        <v>0.78</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.79000000000001</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>49.19</v>
+        <v>49.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>52.61</v>
+        <v>52.35</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.8</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="BD8" t="n">
-        <v>-1.2</v>
+        <v>-1.07</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-117.08</t>
+          <t>-115.26</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1134677799.139045</t>
+          <t>1134076721.703366</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1060885654.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>361101851</v>
+        <v>509324832.2</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>320446639.8</t>
+          <t>396320471.8</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>788698875.08</v>
+        <v>782128914.8200001</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>40655211</t>
+          <t>113004360</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-74814477.89061035</t>
+          <t>-62243888.64823037</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-48471493.66413736</t>
+          <t>6894352.184859514</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1060885654.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,17 +4205,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41266</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8142.579</t>
+          <t>11750.074</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-27.11</t>
+          <t>-25.33</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.06</v>
+        <v>2.31</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>49.04</v>
+        <v>49.19</v>
       </c>
       <c r="AZ9" t="n">
-        <v>52.89</v>
+        <v>52.61</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.98</v>
+        <v>-0.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-118.51</t>
+          <t>-117.08</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>1134677799.139045</t>
+          <t>1134076721.703366</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>303258012.4</v>
+        <v>361101851</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>304232232.7</t>
+          <t>320446639.8</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>833966853.42</v>
+        <v>788698875.08</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-974220</t>
+          <t>40655211</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-79604111.38633272</t>
+          <t>-74814477.89061035</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-75514297.49612796</t>
+          <t>-48471493.66413736</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41266</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5508.131</t>
+          <t>8142.579</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-27.04</t>
+          <t>-27.11</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>49.12</v>
+        <v>49.04</v>
       </c>
       <c r="AZ10" t="n">
-        <v>53.27</v>
+        <v>52.89</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1.06</v>
+        <v>-0.98</v>
       </c>
       <c r="BD10" t="n">
-        <v>-1.38</v>
+        <v>-1.3</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-119.67</t>
+          <t>-118.51</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1134677799.139045</t>
+          <t>1134076721.703366</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>263666319.4</v>
+        <v>303258012.4</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>311360029.6</t>
+          <t>304232232.7</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>893391430.4</v>
+        <v>833966853.42</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-47693710</t>
+          <t>-974220</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-80347713.91182451</t>
+          <t>-79604111.38633272</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-91479905.38125283</t>
+          <t>-75514297.49612796</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41266</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4440.277</t>
+          <t>5508.131</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-23.09</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-27.04</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>64.49</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-1.26</v>
+        <v>0.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>49.17</v>
+        <v>49.12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>53.68</v>
+        <v>53.27</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-1.16</v>
+        <v>-1.06</v>
       </c>
       <c r="BD11" t="n">
-        <v>-1.46</v>
+        <v>-1.38</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-120.81</t>
+          <t>-119.67</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1134677799.139045</t>
+          <t>1134076721.703366</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>267060943</v>
+        <v>263666319.4</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>347232794.8</t>
+          <t>311360029.6</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>1007913686.44</v>
+        <v>893391430.4</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-80171851</t>
+          <t>-47693710</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-78323679.09920117</t>
+          <t>-80347713.91182451</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-96825149.70352924</t>
+          <t>-91479905.38125283</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>217311791.0</t>
+          <t>272351575.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41266</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6477.386</t>
+          <t>4440.277</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-31.98</t>
+          <t>-23.09</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-27.48</t>
+          <t>-28.15</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>64.49</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-0.29</v>
+        <v>-1.26</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.28</v>
+        <v>-0.1</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-8.4</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>49.23</v>
+        <v>49.17</v>
       </c>
       <c r="AZ12" t="n">
-        <v>54.08</v>
+        <v>53.68</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>22.44</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1.19</v>
+        <v>-1.16</v>
       </c>
       <c r="BD12" t="n">
-        <v>-1.54</v>
+        <v>-1.46</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-121.89</t>
+          <t>-120.81</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1134677799.139045</t>
+          <t>1134076721.703366</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>283316111.4</v>
+        <v>267060943</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>416505686.8</t>
+          <t>347232794.8</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>1087982910.56</v>
+        <v>1007913686.44</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-133189575</t>
+          <t>-80171851</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-74959775.3529597</t>
+          <t>-78323679.09920117</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-95106052.24594092</t>
+          <t>-96825149.70352924</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>319770748.0</t>
+          <t>217311791.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41266</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/軟體開發工具.xlsx
+++ b/Result/checksun_type/軟體開發工具.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9557.26</t>
+          <t>9281.266</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>-22.08</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.81</t>
+          <t>-26.74</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-2.53</v>
+        <v>-1.87</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-9.66</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>50.68</t>
+          <t>50.39</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>49.64</v>
+        <v>49.66</v>
       </c>
       <c r="AZ2" t="n">
-        <v>51.16</v>
+        <v>50.9</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>62.47</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.38</v>
+        <v>-0.34</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-105.34</t>
+          <t>-104.83</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1134076721.703366</t>
+          <t>1133458090.182773</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>470739725.0</t>
+          <t>461582544.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>1059769638.2</v>
+        <v>681525236.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>855744091.9</t>
+          <t>874667188.8</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>721014826.84</v>
+        <v>703940053.86</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>204025546</t>
+          <t>-193141952</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>35299585.55361911</t>
+          <t>30075060.44003008</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>29104814.08141351</t>
+          <t>1340172.315290451</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>470739725.0</t>
+          <t>461582544.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>41266</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6918.145</t>
+          <t>9557.26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.78</t>
+          <t>-26.81</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>67.86</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-2.07</v>
+        <v>-2.53</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.12</v>
+        <v>2.1</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-9.66</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>51.16</t>
+          <t>50.68</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>49.61</v>
+        <v>49.64</v>
       </c>
       <c r="AZ3" t="n">
-        <v>51.39</v>
+        <v>51.16</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>56.69</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>62.47</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.43</v>
+        <v>-0.38</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-106.17</t>
+          <t>-105.34</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1134076721.703366</t>
+          <t>1133458090.182773</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>346535516.0</t>
+          <t>470739725.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>1151477764.8</v>
+        <v>1059769638.2</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>830401298.5</t>
+          <t>855744091.9</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>751453437.48</v>
+        <v>721014826.84</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>321076466</t>
+          <t>204025546</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>36425907.63947468</t>
+          <t>35299585.55361911</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>66748003.8515389</t>
+          <t>29104814.08141351</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>346535516.0</t>
+          <t>470739725.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>41266</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16550.342</t>
+          <t>6918.145</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>56.37</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.44</t>
+          <t>-25.78</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>81.39</t>
+          <t>67.86</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-0.89</v>
+        <v>-2.07</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-9.35</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>51.46</t>
+          <t>51.16</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>49.67</v>
+        <v>49.61</v>
       </c>
       <c r="AZ4" t="n">
-        <v>51.59</v>
+        <v>51.39</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>56.78</t>
+          <t>56.69</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>94.04</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.53</v>
+        <v>-0.43</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-107.49</t>
+          <t>-106.17</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1134076721.703366</t>
+          <t>1133458090.182773</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>852127658.0</t>
+          <t>346535516.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>1294347792.4</v>
+        <v>1151477764.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>827724821.7</t>
+          <t>830401298.5</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>763148823</v>
+        <v>751453437.48</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>466622970</t>
+          <t>321076466</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>30912799.23728118</t>
+          <t>36425907.63947468</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>131447725.7784487</t>
+          <t>66748003.8515389</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>852127658.0</t>
+          <t>346535516.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,17 +2277,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>41266</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24262.603</t>
+          <t>16550.342</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,172 +2404,172 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-3.13</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>56.37</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-07-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-01-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>41.8</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>48.8</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>48.05</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-24.44</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-13.01</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/07/01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>39.05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-5.26</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>60.75</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-07-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-01-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025/07/03</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>39.1</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>67.5</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>48.05</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-22.96</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-13.01</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/07/01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>39.05</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/07/03</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>39.1</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>47.5</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/09/10</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,50 +2580,50 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>81.39</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1.29</v>
+        <v>-0.89</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>51.34</t>
+          <t>51.46</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>49.66</v>
+        <v>49.67</v>
       </c>
       <c r="AZ5" t="n">
-        <v>51.76</v>
+        <v>51.59</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2632,14 +2632,14 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>87.16</t>
+          <t>94.04</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.65</v>
+        <v>-0.53</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-109.26</t>
+          <t>-107.49</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1134076721.703366</t>
+          <t>1133458090.182773</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>1276640741.0</t>
+          <t>852127658.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>1242168469.4</v>
+        <v>1294347792.4</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>772713240.9</t>
+          <t>827724821.7</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>766248058.12</v>
+        <v>763148823</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>469455228</t>
+          <t>466622970</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>12633721.68434163</t>
+          <t>30912799.23728118</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>165010751.6819468</t>
+          <t>131447725.7784487</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>1276640741.0</t>
+          <t>852127658.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>41266</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
+          <t>50.5</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
           <t>51.0</t>
-        </is>
-      </c>
-      <c r="CS5" t="inlineStr">
-        <is>
-          <t>52.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44624.702</t>
+          <t>24262.603</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>60.39</t>
+          <t>60.75</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.59</t>
+          <t>-22.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,17 +3062,17 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3081,47 +3081,47 @@
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.24</v>
+        <v>1.29</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.37</v>
+        <v>3.38</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>51.34</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>49.6</v>
+        <v>49.66</v>
       </c>
       <c r="AZ6" t="n">
-        <v>51.91</v>
+        <v>51.76</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>56.78</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>87.16</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.25</v>
+        <v>-0.08</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.79</v>
+        <v>-0.65</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-111.27</t>
+          <t>-109.26</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1134076721.703366</t>
+          <t>1133458090.182773</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>2352804551.0</t>
+          <t>1276640741.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>1067809140.8</v>
+        <v>1242168469.4</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>665737730.1</t>
+          <t>772713240.9</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>775901935.04</v>
+        <v>766248058.12</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>402071410</t>
+          <t>469455228</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-15071192.86067748</t>
+          <t>12633721.68434163</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>161581145.8054459</t>
+          <t>165010751.6819468</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>2352804551.0</t>
+          <t>1276640741.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,17 +3241,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>41266</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17888.375</t>
+          <t>44624.702</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>60.39</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-24.59</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>2.68</v>
+        <v>0.24</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.63</v>
+        <v>2.37</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>50.45</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>49.64</v>
+        <v>49.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>52.11</v>
+        <v>51.91</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>56.72</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>62.45</t>
+          <t>68.37</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.35</v>
+        <v>-0.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.93</v>
+        <v>-0.79</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-113.20</t>
+          <t>-111.27</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1134076721.703366</t>
+          <t>1133458090.182773</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>929280358.0</t>
+          <t>2352804551.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>651718545.6</v>
+        <v>1067809140.8</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>459389744.3</t>
+          <t>665737730.1</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>772359077.74</v>
+        <v>775901935.04</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>192328801</t>
+          <t>402071410</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-47189799.89088174</t>
+          <t>-15071192.86067748</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>35607688.27453578</t>
+          <t>161581145.8054459</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>929280358.0</t>
+          <t>2352804551.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>41266</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20739.776</t>
+          <t>17888.375</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4041,51 +4041,51 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>3.64</v>
+        <v>2.68</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.78</v>
+        <v>1.63</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>49.79000000000001</t>
+          <t>50.45</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>49.4</v>
+        <v>49.64</v>
       </c>
       <c r="AZ8" t="n">
-        <v>52.35</v>
+        <v>52.11</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.62</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>62.45</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="BD8" t="n">
-        <v>-1.07</v>
+        <v>-0.93</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-115.26</t>
+          <t>-113.20</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1134076721.703366</t>
+          <t>1133458090.182773</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>1060885654.0</t>
+          <t>929280358.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>509324832.2</v>
+        <v>651718545.6</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>396320471.8</t>
+          <t>459389744.3</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>782128914.8200001</v>
+        <v>772359077.74</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>113004360</t>
+          <t>192328801</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-62243888.64823037</t>
+          <t>-47189799.89088174</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>6894352.184859514</t>
+          <t>35607688.27453578</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>1060885654.0</t>
+          <t>929280358.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>28.68</t>
+          <t>29.18</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>41266</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
           <t>51.8</t>
-        </is>
-      </c>
-      <c r="CR8" t="inlineStr">
-        <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="CS8" t="inlineStr">
-        <is>
-          <t>51.6</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11750.074</t>
+          <t>20739.776</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-25.33</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,12 +4508,12 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4523,51 +4523,51 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>2.31</v>
+        <v>3.64</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.15</v>
+        <v>0.78</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.79000000000001</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>49.19</v>
+        <v>49.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>52.61</v>
+        <v>52.35</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.8</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="BD9" t="n">
-        <v>-1.2</v>
+        <v>-1.07</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-117.08</t>
+          <t>-115.26</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>1134076721.703366</t>
+          <t>1133458090.182773</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1060885654.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>361101851</v>
+        <v>509324832.2</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>320446639.8</t>
+          <t>396320471.8</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>788698875.08</v>
+        <v>782128914.8200001</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>40655211</t>
+          <t>113004360</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-74814477.89061035</t>
+          <t>-62243888.64823037</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-48471493.66413736</t>
+          <t>6894352.184859514</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>591231043.0</t>
+          <t>1060885654.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>28.68</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>41266</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8142.579</t>
+          <t>11750.074</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-27.11</t>
+          <t>-25.33</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.06</v>
+        <v>2.31</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>49.04</v>
+        <v>49.19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>52.89</v>
+        <v>52.61</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.98</v>
+        <v>-0.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-118.51</t>
+          <t>-117.08</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1134076721.703366</t>
+          <t>1133458090.182773</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>303258012.4</v>
+        <v>361101851</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>304232232.7</t>
+          <t>320446639.8</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>833966853.42</v>
+        <v>788698875.08</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-974220</t>
+          <t>40655211</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-79604111.38633272</t>
+          <t>-74814477.89061035</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-75514297.49612796</t>
+          <t>-48471493.66413736</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>404844098.0</t>
+          <t>591231043.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,17 +5169,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>41266</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5508.131</t>
+          <t>8142.579</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-27.04</t>
+          <t>-27.11</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>49.12</v>
+        <v>49.04</v>
       </c>
       <c r="AZ11" t="n">
-        <v>53.27</v>
+        <v>52.89</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>23.29</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-1.06</v>
+        <v>-0.98</v>
       </c>
       <c r="BD11" t="n">
-        <v>-1.38</v>
+        <v>-1.3</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-119.67</t>
+          <t>-118.51</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1134076721.703366</t>
+          <t>1133458090.182773</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>263666319.4</v>
+        <v>303258012.4</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>311360029.6</t>
+          <t>304232232.7</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>893391430.4</v>
+        <v>833966853.42</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-47693710</t>
+          <t>-974220</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-80347713.91182451</t>
+          <t>-79604111.38633272</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-91479905.38125283</t>
+          <t>-75514297.49612796</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>272351575.0</t>
+          <t>404844098.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>41266</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5753,7 +5753,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4440.277</t>
+          <t>5508.131</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-23.09</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-28.15</t>
+          <t>-27.04</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>36.96</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>64.49</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-1.26</v>
+        <v>0.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>49.17</v>
+        <v>49.12</v>
       </c>
       <c r="AZ12" t="n">
-        <v>53.68</v>
+        <v>53.27</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>23.29</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1.16</v>
+        <v>-1.06</v>
       </c>
       <c r="BD12" t="n">
-        <v>-1.46</v>
+        <v>-1.38</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-120.81</t>
+      